--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_Fiets.xlsx
@@ -388,10 +388,10 @@
         <v>15389</v>
       </c>
       <c r="C2">
-        <v>23037</v>
+        <v>23042</v>
       </c>
       <c r="D2">
-        <v>47688</v>
+        <v>47694</v>
       </c>
       <c r="E2">
         <v>68528</v>
@@ -405,10 +405,10 @@
         <v>15933</v>
       </c>
       <c r="C3">
-        <v>25719</v>
+        <v>25724</v>
       </c>
       <c r="D3">
-        <v>52890</v>
+        <v>52898</v>
       </c>
       <c r="E3">
         <v>73632</v>
@@ -422,13 +422,13 @@
         <v>13679</v>
       </c>
       <c r="C4">
-        <v>22314</v>
+        <v>22315</v>
       </c>
       <c r="D4">
-        <v>49054</v>
+        <v>49059</v>
       </c>
       <c r="E4">
-        <v>69860</v>
+        <v>69871</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>13679</v>
       </c>
       <c r="C5">
-        <v>22314</v>
+        <v>22315</v>
       </c>
       <c r="D5">
-        <v>49054</v>
+        <v>49059</v>
       </c>
       <c r="E5">
-        <v>69860</v>
+        <v>69871</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>13679</v>
       </c>
       <c r="C6">
-        <v>22314</v>
+        <v>22315</v>
       </c>
       <c r="D6">
-        <v>49054</v>
+        <v>49059</v>
       </c>
       <c r="E6">
-        <v>69860</v>
+        <v>69871</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>13561</v>
       </c>
       <c r="C7">
-        <v>20466</v>
+        <v>20496</v>
       </c>
       <c r="D7">
-        <v>44465</v>
+        <v>44510</v>
       </c>
       <c r="E7">
-        <v>64411</v>
+        <v>64461</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>13561</v>
       </c>
       <c r="C8">
-        <v>20466</v>
+        <v>20496</v>
       </c>
       <c r="D8">
-        <v>44465</v>
+        <v>44510</v>
       </c>
       <c r="E8">
-        <v>64411</v>
+        <v>64461</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>11560</v>
       </c>
       <c r="C9">
-        <v>16494</v>
+        <v>16547</v>
       </c>
       <c r="D9">
-        <v>36732</v>
+        <v>36858</v>
       </c>
       <c r="E9">
-        <v>56029</v>
+        <v>56184</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>13561</v>
       </c>
       <c r="C10">
-        <v>20466</v>
+        <v>20496</v>
       </c>
       <c r="D10">
-        <v>44465</v>
+        <v>44510</v>
       </c>
       <c r="E10">
-        <v>64411</v>
+        <v>64461</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>13561</v>
       </c>
       <c r="C11">
-        <v>20466</v>
+        <v>20496</v>
       </c>
       <c r="D11">
-        <v>44465</v>
+        <v>44510</v>
       </c>
       <c r="E11">
-        <v>64411</v>
+        <v>64461</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,10 +558,10 @@
         <v>12784</v>
       </c>
       <c r="C12">
-        <v>21103</v>
+        <v>21105</v>
       </c>
       <c r="D12">
-        <v>47116</v>
+        <v>47122</v>
       </c>
       <c r="E12">
         <v>68735</v>
@@ -575,10 +575,10 @@
         <v>15933</v>
       </c>
       <c r="C13">
-        <v>25719</v>
+        <v>25724</v>
       </c>
       <c r="D13">
-        <v>52890</v>
+        <v>52898</v>
       </c>
       <c r="E13">
         <v>73632</v>
@@ -592,10 +592,10 @@
         <v>12784</v>
       </c>
       <c r="C14">
-        <v>21103</v>
+        <v>21105</v>
       </c>
       <c r="D14">
-        <v>47116</v>
+        <v>47122</v>
       </c>
       <c r="E14">
         <v>68735</v>
@@ -609,13 +609,13 @@
         <v>13561</v>
       </c>
       <c r="C15">
-        <v>20466</v>
+        <v>20496</v>
       </c>
       <c r="D15">
-        <v>44465</v>
+        <v>44510</v>
       </c>
       <c r="E15">
-        <v>64411</v>
+        <v>64461</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>13411</v>
       </c>
       <c r="C16">
-        <v>18772</v>
+        <v>18787</v>
       </c>
       <c r="D16">
-        <v>39984</v>
+        <v>40022</v>
       </c>
       <c r="E16">
-        <v>58987</v>
+        <v>59024</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,10 +643,10 @@
         <v>12784</v>
       </c>
       <c r="C17">
-        <v>21103</v>
+        <v>21105</v>
       </c>
       <c r="D17">
-        <v>47116</v>
+        <v>47122</v>
       </c>
       <c r="E17">
         <v>68735</v>
@@ -660,10 +660,10 @@
         <v>15933</v>
       </c>
       <c r="C18">
-        <v>25719</v>
+        <v>25724</v>
       </c>
       <c r="D18">
-        <v>52890</v>
+        <v>52898</v>
       </c>
       <c r="E18">
         <v>73632</v>
@@ -677,13 +677,13 @@
         <v>13411</v>
       </c>
       <c r="C19">
-        <v>18772</v>
+        <v>18787</v>
       </c>
       <c r="D19">
-        <v>39984</v>
+        <v>40022</v>
       </c>
       <c r="E19">
-        <v>58987</v>
+        <v>59024</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>13411</v>
       </c>
       <c r="C20">
-        <v>18772</v>
+        <v>18787</v>
       </c>
       <c r="D20">
-        <v>39984</v>
+        <v>40022</v>
       </c>
       <c r="E20">
-        <v>58987</v>
+        <v>59024</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>13411</v>
       </c>
       <c r="C21">
-        <v>18772</v>
+        <v>18787</v>
       </c>
       <c r="D21">
-        <v>39984</v>
+        <v>40022</v>
       </c>
       <c r="E21">
-        <v>58987</v>
+        <v>59024</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -728,13 +728,13 @@
         <v>21815</v>
       </c>
       <c r="C22">
-        <v>34390</v>
+        <v>34397</v>
       </c>
       <c r="D22">
-        <v>62011</v>
+        <v>62021</v>
       </c>
       <c r="E22">
-        <v>79268</v>
+        <v>79288</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,10 +745,10 @@
         <v>15389</v>
       </c>
       <c r="C23">
-        <v>23037</v>
+        <v>23042</v>
       </c>
       <c r="D23">
-        <v>47688</v>
+        <v>47694</v>
       </c>
       <c r="E23">
         <v>68528</v>
@@ -762,13 +762,13 @@
         <v>10812</v>
       </c>
       <c r="C24">
-        <v>17099</v>
+        <v>17100</v>
       </c>
       <c r="D24">
-        <v>39250</v>
+        <v>39252</v>
       </c>
       <c r="E24">
-        <v>59364</v>
+        <v>59370</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>10812</v>
       </c>
       <c r="C25">
-        <v>17099</v>
+        <v>17100</v>
       </c>
       <c r="D25">
-        <v>39250</v>
+        <v>39252</v>
       </c>
       <c r="E25">
-        <v>59364</v>
+        <v>59370</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -796,13 +796,13 @@
         <v>10812</v>
       </c>
       <c r="C26">
-        <v>17099</v>
+        <v>17100</v>
       </c>
       <c r="D26">
-        <v>39250</v>
+        <v>39252</v>
       </c>
       <c r="E26">
-        <v>59364</v>
+        <v>59370</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -813,13 +813,13 @@
         <v>16199</v>
       </c>
       <c r="C27">
-        <v>24543</v>
+        <v>24544</v>
       </c>
       <c r="D27">
-        <v>50872</v>
+        <v>50876</v>
       </c>
       <c r="E27">
-        <v>71057</v>
+        <v>71068</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -830,13 +830,13 @@
         <v>16199</v>
       </c>
       <c r="C28">
-        <v>24543</v>
+        <v>24544</v>
       </c>
       <c r="D28">
-        <v>50872</v>
+        <v>50876</v>
       </c>
       <c r="E28">
-        <v>71057</v>
+        <v>71068</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -847,13 +847,13 @@
         <v>16199</v>
       </c>
       <c r="C29">
-        <v>24543</v>
+        <v>24544</v>
       </c>
       <c r="D29">
-        <v>50872</v>
+        <v>50876</v>
       </c>
       <c r="E29">
-        <v>71057</v>
+        <v>71068</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>27376</v>
       </c>
       <c r="C30">
-        <v>35567</v>
+        <v>35698</v>
       </c>
       <c r="D30">
-        <v>54021</v>
+        <v>54343</v>
       </c>
       <c r="E30">
-        <v>68834</v>
+        <v>69046</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>27376</v>
       </c>
       <c r="C31">
-        <v>35567</v>
+        <v>35698</v>
       </c>
       <c r="D31">
-        <v>54021</v>
+        <v>54343</v>
       </c>
       <c r="E31">
-        <v>68834</v>
+        <v>69046</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>31024</v>
       </c>
       <c r="C32">
-        <v>40862</v>
+        <v>40930</v>
       </c>
       <c r="D32">
-        <v>60603</v>
+        <v>60726</v>
       </c>
       <c r="E32">
-        <v>74709</v>
+        <v>74770</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>27376</v>
       </c>
       <c r="C33">
-        <v>35567</v>
+        <v>35698</v>
       </c>
       <c r="D33">
-        <v>54021</v>
+        <v>54343</v>
       </c>
       <c r="E33">
-        <v>68834</v>
+        <v>69046</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>40380</v>
+        <v>40391</v>
       </c>
       <c r="C34">
-        <v>51283</v>
+        <v>51301</v>
       </c>
       <c r="D34">
-        <v>70705</v>
+        <v>70720</v>
       </c>
       <c r="E34">
-        <v>83642</v>
+        <v>83653</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,10 +949,10 @@
         <v>39444</v>
       </c>
       <c r="C35">
-        <v>50359</v>
+        <v>50369</v>
       </c>
       <c r="D35">
-        <v>69350</v>
+        <v>69373</v>
       </c>
       <c r="E35">
         <v>83059</v>
@@ -966,13 +966,13 @@
         <v>25626</v>
       </c>
       <c r="C36">
-        <v>35226</v>
+        <v>35234</v>
       </c>
       <c r="D36">
-        <v>56510</v>
+        <v>56604</v>
       </c>
       <c r="E36">
-        <v>71859</v>
+        <v>71927</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>28201</v>
       </c>
       <c r="C37">
-        <v>35781</v>
+        <v>35811</v>
       </c>
       <c r="D37">
-        <v>53481</v>
+        <v>53763</v>
       </c>
       <c r="E37">
-        <v>68064</v>
+        <v>68261</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>28201</v>
       </c>
       <c r="C38">
-        <v>35781</v>
+        <v>35811</v>
       </c>
       <c r="D38">
-        <v>53481</v>
+        <v>53763</v>
       </c>
       <c r="E38">
-        <v>68064</v>
+        <v>68261</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>35501</v>
+        <v>35524</v>
       </c>
       <c r="C39">
-        <v>44656</v>
+        <v>44747</v>
       </c>
       <c r="D39">
-        <v>63363</v>
+        <v>63463</v>
       </c>
       <c r="E39">
-        <v>77024</v>
+        <v>77074</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>41153</v>
       </c>
       <c r="C40">
-        <v>52044</v>
+        <v>52049</v>
       </c>
       <c r="D40">
-        <v>71312</v>
+        <v>71328</v>
       </c>
       <c r="E40">
-        <v>83957</v>
+        <v>83967</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,10 +1051,10 @@
         <v>39444</v>
       </c>
       <c r="C41">
-        <v>50359</v>
+        <v>50369</v>
       </c>
       <c r="D41">
-        <v>69350</v>
+        <v>69373</v>
       </c>
       <c r="E41">
         <v>83059</v>
@@ -1068,13 +1068,13 @@
         <v>28676</v>
       </c>
       <c r="C42">
-        <v>37930</v>
+        <v>37939</v>
       </c>
       <c r="D42">
-        <v>57771</v>
+        <v>57875</v>
       </c>
       <c r="E42">
-        <v>72196</v>
+        <v>72258</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,10 +1085,10 @@
         <v>32198</v>
       </c>
       <c r="C43">
-        <v>43666</v>
+        <v>43670</v>
       </c>
       <c r="D43">
-        <v>64061</v>
+        <v>64085</v>
       </c>
       <c r="E43">
         <v>78857</v>
@@ -1102,13 +1102,13 @@
         <v>32606</v>
       </c>
       <c r="C44">
-        <v>45153</v>
+        <v>45163</v>
       </c>
       <c r="D44">
-        <v>66506</v>
+        <v>66526</v>
       </c>
       <c r="E44">
-        <v>80437</v>
+        <v>80456</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>25494</v>
       </c>
       <c r="C45">
-        <v>34339</v>
+        <v>34343</v>
       </c>
       <c r="D45">
-        <v>54839</v>
+        <v>54925</v>
       </c>
       <c r="E45">
-        <v>70000</v>
+        <v>70061</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>31537</v>
       </c>
       <c r="C46">
-        <v>40774</v>
+        <v>40793</v>
       </c>
       <c r="D46">
-        <v>60024</v>
+        <v>60136</v>
       </c>
       <c r="E46">
-        <v>74048</v>
+        <v>74106</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>30670</v>
       </c>
       <c r="C47">
-        <v>43033</v>
+        <v>43035</v>
       </c>
       <c r="D47">
-        <v>65016</v>
+        <v>65031</v>
       </c>
       <c r="E47">
-        <v>79577</v>
+        <v>79597</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,10 +1170,10 @@
         <v>28668</v>
       </c>
       <c r="C48">
-        <v>40098</v>
+        <v>40100</v>
       </c>
       <c r="D48">
-        <v>61512</v>
+        <v>61531</v>
       </c>
       <c r="E48">
         <v>77062</v>
@@ -1187,13 +1187,13 @@
         <v>14523</v>
       </c>
       <c r="C49">
-        <v>19328</v>
+        <v>19363</v>
       </c>
       <c r="D49">
-        <v>37802</v>
+        <v>37839</v>
       </c>
       <c r="E49">
-        <v>54440</v>
+        <v>54470</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1207,7 +1207,7 @@
         <v>20502</v>
       </c>
       <c r="D50">
-        <v>41220</v>
+        <v>41225</v>
       </c>
       <c r="E50">
         <v>61130</v>
@@ -1221,10 +1221,10 @@
         <v>13144</v>
       </c>
       <c r="C51">
-        <v>18928</v>
+        <v>18932</v>
       </c>
       <c r="D51">
-        <v>38546</v>
+        <v>38551</v>
       </c>
       <c r="E51">
         <v>56978</v>
@@ -1238,10 +1238,10 @@
         <v>14195</v>
       </c>
       <c r="C52">
-        <v>20564</v>
+        <v>20571</v>
       </c>
       <c r="D52">
-        <v>41496</v>
+        <v>41502</v>
       </c>
       <c r="E52">
         <v>60499</v>
@@ -1255,13 +1255,13 @@
         <v>12052</v>
       </c>
       <c r="C53">
-        <v>16421</v>
+        <v>16433</v>
       </c>
       <c r="D53">
-        <v>33620</v>
+        <v>33653</v>
       </c>
       <c r="E53">
-        <v>49576</v>
+        <v>49601</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>11395</v>
       </c>
       <c r="C54">
-        <v>15739</v>
+        <v>15749</v>
       </c>
       <c r="D54">
-        <v>32583</v>
+        <v>32615</v>
       </c>
       <c r="E54">
-        <v>48059</v>
+        <v>48084</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1292,7 +1292,7 @@
         <v>20502</v>
       </c>
       <c r="D55">
-        <v>41220</v>
+        <v>41225</v>
       </c>
       <c r="E55">
         <v>61130</v>
@@ -1306,10 +1306,10 @@
         <v>18288</v>
       </c>
       <c r="C56">
-        <v>25699</v>
+        <v>25709</v>
       </c>
       <c r="D56">
-        <v>48579</v>
+        <v>48585</v>
       </c>
       <c r="E56">
         <v>67612</v>
@@ -1323,13 +1323,13 @@
         <v>13660</v>
       </c>
       <c r="C57">
-        <v>19524</v>
+        <v>19526</v>
       </c>
       <c r="D57">
-        <v>40541</v>
+        <v>40544</v>
       </c>
       <c r="E57">
-        <v>59918</v>
+        <v>59924</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1340,13 +1340,13 @@
         <v>17051</v>
       </c>
       <c r="C58">
-        <v>23673</v>
+        <v>23674</v>
       </c>
       <c r="D58">
-        <v>47931</v>
+        <v>47933</v>
       </c>
       <c r="E58">
-        <v>68335</v>
+        <v>68343</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1357,13 +1357,13 @@
         <v>17051</v>
       </c>
       <c r="C59">
-        <v>23673</v>
+        <v>23674</v>
       </c>
       <c r="D59">
-        <v>47931</v>
+        <v>47933</v>
       </c>
       <c r="E59">
-        <v>68335</v>
+        <v>68343</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1377,10 +1377,10 @@
         <v>15780</v>
       </c>
       <c r="D60">
-        <v>36884</v>
+        <v>36886</v>
       </c>
       <c r="E60">
-        <v>56650</v>
+        <v>56655</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1394,10 +1394,10 @@
         <v>15780</v>
       </c>
       <c r="D61">
-        <v>36884</v>
+        <v>36886</v>
       </c>
       <c r="E61">
-        <v>56650</v>
+        <v>56655</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1411,10 +1411,10 @@
         <v>10915</v>
       </c>
       <c r="D62">
-        <v>32146</v>
+        <v>32147</v>
       </c>
       <c r="E62">
-        <v>52906</v>
+        <v>52909</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1428,10 +1428,10 @@
         <v>10915</v>
       </c>
       <c r="D63">
-        <v>32146</v>
+        <v>32147</v>
       </c>
       <c r="E63">
-        <v>52906</v>
+        <v>52909</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>4424</v>
       </c>
       <c r="C64">
-        <v>9515</v>
+        <v>9516</v>
       </c>
       <c r="D64">
-        <v>30202</v>
+        <v>30204</v>
       </c>
       <c r="E64">
-        <v>50491</v>
+        <v>50494</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>4424</v>
       </c>
       <c r="C65">
-        <v>9515</v>
+        <v>9516</v>
       </c>
       <c r="D65">
-        <v>30202</v>
+        <v>30204</v>
       </c>
       <c r="E65">
-        <v>50491</v>
+        <v>50494</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>17922</v>
       </c>
       <c r="C66">
-        <v>28992</v>
+        <v>29027</v>
       </c>
       <c r="D66">
-        <v>53229</v>
+        <v>53327</v>
       </c>
       <c r="E66">
-        <v>69705</v>
+        <v>69785</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,10 +1493,10 @@
         <v>22082</v>
       </c>
       <c r="C67">
-        <v>36273</v>
+        <v>36281</v>
       </c>
       <c r="D67">
-        <v>61008</v>
+        <v>61029</v>
       </c>
       <c r="E67">
         <v>77248</v>
@@ -1510,13 +1510,13 @@
         <v>17922</v>
       </c>
       <c r="C68">
-        <v>28992</v>
+        <v>29027</v>
       </c>
       <c r="D68">
-        <v>53229</v>
+        <v>53327</v>
       </c>
       <c r="E68">
-        <v>69705</v>
+        <v>69785</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,10 +1527,10 @@
         <v>22082</v>
       </c>
       <c r="C69">
-        <v>36273</v>
+        <v>36281</v>
       </c>
       <c r="D69">
-        <v>61008</v>
+        <v>61029</v>
       </c>
       <c r="E69">
         <v>77248</v>
@@ -1544,10 +1544,10 @@
         <v>22082</v>
       </c>
       <c r="C70">
-        <v>36273</v>
+        <v>36281</v>
       </c>
       <c r="D70">
-        <v>61008</v>
+        <v>61029</v>
       </c>
       <c r="E70">
         <v>77248</v>
@@ -1561,13 +1561,13 @@
         <v>26378</v>
       </c>
       <c r="C71">
-        <v>41418</v>
+        <v>41423</v>
       </c>
       <c r="D71">
-        <v>65814</v>
+        <v>65836</v>
       </c>
       <c r="E71">
-        <v>80272</v>
+        <v>80295</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>23830</v>
       </c>
       <c r="C72">
-        <v>38314</v>
+        <v>38318</v>
       </c>
       <c r="D72">
-        <v>63150</v>
+        <v>63169</v>
       </c>
       <c r="E72">
-        <v>78232</v>
+        <v>78255</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>23830</v>
       </c>
       <c r="C73">
-        <v>38314</v>
+        <v>38318</v>
       </c>
       <c r="D73">
-        <v>63150</v>
+        <v>63169</v>
       </c>
       <c r="E73">
-        <v>78232</v>
+        <v>78255</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>23830</v>
       </c>
       <c r="C74">
-        <v>38314</v>
+        <v>38318</v>
       </c>
       <c r="D74">
-        <v>63150</v>
+        <v>63169</v>
       </c>
       <c r="E74">
-        <v>78232</v>
+        <v>78255</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1632,10 +1632,10 @@
         <v>27479</v>
       </c>
       <c r="D75">
-        <v>53304</v>
+        <v>53310</v>
       </c>
       <c r="E75">
-        <v>70508</v>
+        <v>70525</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,10 +1646,10 @@
         <v>22082</v>
       </c>
       <c r="C76">
-        <v>36273</v>
+        <v>36281</v>
       </c>
       <c r="D76">
-        <v>61008</v>
+        <v>61029</v>
       </c>
       <c r="E76">
         <v>77248</v>
@@ -1663,13 +1663,13 @@
         <v>22019</v>
       </c>
       <c r="C77">
-        <v>36135</v>
+        <v>36137</v>
       </c>
       <c r="D77">
-        <v>61586</v>
+        <v>61601</v>
       </c>
       <c r="E77">
-        <v>77213</v>
+        <v>77235</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>22019</v>
       </c>
       <c r="C78">
-        <v>36135</v>
+        <v>36137</v>
       </c>
       <c r="D78">
-        <v>61586</v>
+        <v>61601</v>
       </c>
       <c r="E78">
-        <v>77213</v>
+        <v>77235</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>22019</v>
       </c>
       <c r="C79">
-        <v>36135</v>
+        <v>36137</v>
       </c>
       <c r="D79">
-        <v>61586</v>
+        <v>61601</v>
       </c>
       <c r="E79">
-        <v>77213</v>
+        <v>77235</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>22019</v>
       </c>
       <c r="C80">
-        <v>36135</v>
+        <v>36137</v>
       </c>
       <c r="D80">
-        <v>61586</v>
+        <v>61601</v>
       </c>
       <c r="E80">
-        <v>77213</v>
+        <v>77235</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>32015</v>
       </c>
       <c r="C81">
-        <v>44764</v>
+        <v>44775</v>
       </c>
       <c r="D81">
-        <v>66199</v>
+        <v>66215</v>
       </c>
       <c r="E81">
-        <v>79792</v>
+        <v>79812</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>32015</v>
       </c>
       <c r="C82">
-        <v>44764</v>
+        <v>44775</v>
       </c>
       <c r="D82">
-        <v>66199</v>
+        <v>66215</v>
       </c>
       <c r="E82">
-        <v>79792</v>
+        <v>79812</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1768,10 +1768,10 @@
         <v>34953</v>
       </c>
       <c r="D83">
-        <v>58235</v>
+        <v>58241</v>
       </c>
       <c r="E83">
-        <v>72833</v>
+        <v>72852</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1785,10 +1785,10 @@
         <v>34953</v>
       </c>
       <c r="D84">
-        <v>58235</v>
+        <v>58241</v>
       </c>
       <c r="E84">
-        <v>72833</v>
+        <v>72852</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>35987</v>
       </c>
       <c r="C85">
-        <v>48435</v>
+        <v>48436</v>
       </c>
       <c r="D85">
-        <v>68025</v>
+        <v>68041</v>
       </c>
       <c r="E85">
-        <v>80207</v>
+        <v>80225</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>35987</v>
       </c>
       <c r="C86">
-        <v>48435</v>
+        <v>48436</v>
       </c>
       <c r="D86">
-        <v>68025</v>
+        <v>68041</v>
       </c>
       <c r="E86">
-        <v>80207</v>
+        <v>80225</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>34396</v>
       </c>
       <c r="C87">
-        <v>48118</v>
+        <v>48128</v>
       </c>
       <c r="D87">
-        <v>68779</v>
+        <v>68798</v>
       </c>
       <c r="E87">
-        <v>81158</v>
+        <v>81177</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>34396</v>
       </c>
       <c r="C88">
-        <v>48118</v>
+        <v>48128</v>
       </c>
       <c r="D88">
-        <v>68779</v>
+        <v>68798</v>
       </c>
       <c r="E88">
-        <v>81158</v>
+        <v>81177</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>34396</v>
       </c>
       <c r="C89">
-        <v>48118</v>
+        <v>48128</v>
       </c>
       <c r="D89">
-        <v>68779</v>
+        <v>68798</v>
       </c>
       <c r="E89">
-        <v>81158</v>
+        <v>81177</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>44404</v>
+        <v>44405</v>
       </c>
       <c r="C90">
-        <v>50277</v>
+        <v>50617</v>
       </c>
       <c r="D90">
-        <v>62439</v>
+        <v>64209</v>
       </c>
       <c r="E90">
-        <v>72980</v>
+        <v>75111</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>44361</v>
+        <v>44362</v>
       </c>
       <c r="C91">
-        <v>50097</v>
+        <v>50449</v>
       </c>
       <c r="D91">
-        <v>62001</v>
+        <v>63883</v>
       </c>
       <c r="E91">
-        <v>72277</v>
+        <v>74632</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>44179</v>
+        <v>44181</v>
       </c>
       <c r="C92">
-        <v>49327</v>
+        <v>49731</v>
       </c>
       <c r="D92">
-        <v>60131</v>
+        <v>62492</v>
       </c>
       <c r="E92">
-        <v>69275</v>
+        <v>72584</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>44733</v>
+        <v>44734</v>
       </c>
       <c r="C93">
-        <v>51671</v>
+        <v>51915</v>
       </c>
       <c r="D93">
-        <v>65823</v>
+        <v>66725</v>
       </c>
       <c r="E93">
-        <v>78412</v>
+        <v>78818</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1949,16 +1949,16 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>43974</v>
+        <v>43982</v>
       </c>
       <c r="C94">
-        <v>48575</v>
+        <v>48855</v>
       </c>
       <c r="D94">
-        <v>54824</v>
+        <v>57095</v>
       </c>
       <c r="E94">
-        <v>63376</v>
+        <v>67291</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>44703</v>
+        <v>44704</v>
       </c>
       <c r="C95">
-        <v>51543</v>
+        <v>51796</v>
       </c>
       <c r="D95">
-        <v>65515</v>
+        <v>66496</v>
       </c>
       <c r="E95">
-        <v>77916</v>
+        <v>78480</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>44241</v>
+        <v>44242</v>
       </c>
       <c r="C96">
-        <v>49588</v>
+        <v>49975</v>
       </c>
       <c r="D96">
-        <v>60765</v>
+        <v>62964</v>
       </c>
       <c r="E96">
-        <v>70293</v>
+        <v>73278</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>44733</v>
+        <v>44734</v>
       </c>
       <c r="C97">
-        <v>51671</v>
+        <v>51915</v>
       </c>
       <c r="D97">
-        <v>65823</v>
+        <v>66725</v>
       </c>
       <c r="E97">
-        <v>78412</v>
+        <v>78818</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>41823</v>
+        <v>41825</v>
       </c>
       <c r="C98">
-        <v>49344</v>
+        <v>49674</v>
       </c>
       <c r="D98">
-        <v>64577</v>
+        <v>65672</v>
       </c>
       <c r="E98">
-        <v>78021</v>
+        <v>78524</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>41656</v>
+        <v>41658</v>
       </c>
       <c r="C99">
-        <v>48656</v>
+        <v>49039</v>
       </c>
       <c r="D99">
-        <v>62938</v>
+        <v>64461</v>
       </c>
       <c r="E99">
-        <v>75511</v>
+        <v>76827</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>43712</v>
       </c>
       <c r="C100">
-        <v>49892</v>
+        <v>50047</v>
       </c>
       <c r="D100">
-        <v>63283</v>
+        <v>64228</v>
       </c>
       <c r="E100">
-        <v>75411</v>
+        <v>76249</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>43647</v>
       </c>
       <c r="C101">
-        <v>49557</v>
+        <v>49728</v>
       </c>
       <c r="D101">
-        <v>62360</v>
+        <v>63514</v>
       </c>
       <c r="E101">
-        <v>73847</v>
+        <v>75166</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>43773</v>
       </c>
       <c r="C102">
-        <v>50203</v>
+        <v>50344</v>
       </c>
       <c r="D102">
-        <v>64141</v>
+        <v>64891</v>
       </c>
       <c r="E102">
-        <v>76865</v>
+        <v>77256</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2105,13 +2105,13 @@
         <v>39726</v>
       </c>
       <c r="C103">
-        <v>47392</v>
+        <v>47736</v>
       </c>
       <c r="D103">
-        <v>63266</v>
+        <v>64377</v>
       </c>
       <c r="E103">
-        <v>77229</v>
+        <v>77738</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2122,13 +2122,13 @@
         <v>39726</v>
       </c>
       <c r="C104">
-        <v>47392</v>
+        <v>47736</v>
       </c>
       <c r="D104">
-        <v>63266</v>
+        <v>64377</v>
       </c>
       <c r="E104">
-        <v>77229</v>
+        <v>77738</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>42648</v>
       </c>
       <c r="C105">
-        <v>52666</v>
+        <v>52735</v>
       </c>
       <c r="D105">
-        <v>69960</v>
+        <v>70195</v>
       </c>
       <c r="E105">
-        <v>82134</v>
+        <v>82299</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2156,13 +2156,13 @@
         <v>46668</v>
       </c>
       <c r="C106">
-        <v>58607</v>
+        <v>58707</v>
       </c>
       <c r="D106">
-        <v>76367</v>
+        <v>76466</v>
       </c>
       <c r="E106">
-        <v>86761</v>
+        <v>86808</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2173,13 +2173,13 @@
         <v>46668</v>
       </c>
       <c r="C107">
-        <v>58607</v>
+        <v>58707</v>
       </c>
       <c r="D107">
-        <v>76367</v>
+        <v>76466</v>
       </c>
       <c r="E107">
-        <v>86761</v>
+        <v>86808</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,10 +2190,10 @@
         <v>50653</v>
       </c>
       <c r="C108">
-        <v>63832</v>
+        <v>63837</v>
       </c>
       <c r="D108">
-        <v>80479</v>
+        <v>80490</v>
       </c>
       <c r="E108">
         <v>90526</v>
@@ -2204,16 +2204,16 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>40718</v>
+        <v>40721</v>
       </c>
       <c r="C109">
-        <v>51124</v>
+        <v>51322</v>
       </c>
       <c r="D109">
-        <v>68696</v>
+        <v>68983</v>
       </c>
       <c r="E109">
-        <v>81085</v>
+        <v>81256</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2221,16 +2221,16 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>40718</v>
+        <v>40721</v>
       </c>
       <c r="C110">
-        <v>51124</v>
+        <v>51322</v>
       </c>
       <c r="D110">
-        <v>68696</v>
+        <v>68983</v>
       </c>
       <c r="E110">
-        <v>81085</v>
+        <v>81256</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2238,16 +2238,16 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>40402</v>
+        <v>40405</v>
       </c>
       <c r="C111">
-        <v>50294</v>
+        <v>50534</v>
       </c>
       <c r="D111">
-        <v>66942</v>
+        <v>67444</v>
       </c>
       <c r="E111">
-        <v>79062</v>
+        <v>79645</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>39679</v>
+        <v>39692</v>
       </c>
       <c r="C112">
-        <v>47702</v>
+        <v>48236</v>
       </c>
       <c r="D112">
-        <v>63719</v>
+        <v>64937</v>
       </c>
       <c r="E112">
-        <v>77677</v>
+        <v>78179</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>39710</v>
       </c>
       <c r="C113">
-        <v>49945</v>
+        <v>50109</v>
       </c>
       <c r="D113">
-        <v>67719</v>
+        <v>68006</v>
       </c>
       <c r="E113">
-        <v>80300</v>
+        <v>80499</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>44045</v>
       </c>
       <c r="C114">
-        <v>55692</v>
+        <v>55773</v>
       </c>
       <c r="D114">
-        <v>73973</v>
+        <v>74070</v>
       </c>
       <c r="E114">
-        <v>85039</v>
+        <v>85088</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>39627</v>
+        <v>39639</v>
       </c>
       <c r="C115">
-        <v>47506</v>
+        <v>48062</v>
       </c>
       <c r="D115">
-        <v>63276</v>
+        <v>64613</v>
       </c>
       <c r="E115">
-        <v>77021</v>
+        <v>77739</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>39679</v>
+        <v>39692</v>
       </c>
       <c r="C116">
-        <v>47702</v>
+        <v>48236</v>
       </c>
       <c r="D116">
-        <v>63719</v>
+        <v>64937</v>
       </c>
       <c r="E116">
-        <v>77677</v>
+        <v>78179</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>39727</v>
       </c>
       <c r="C117">
-        <v>49991</v>
+        <v>50153</v>
       </c>
       <c r="D117">
-        <v>67821</v>
+        <v>68096</v>
       </c>
       <c r="E117">
-        <v>80419</v>
+        <v>80594</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>50596</v>
       </c>
       <c r="C118">
-        <v>63878</v>
+        <v>63889</v>
       </c>
       <c r="D118">
-        <v>81212</v>
+        <v>81221</v>
       </c>
       <c r="E118">
-        <v>90380</v>
+        <v>90387</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,10 +2377,10 @@
         <v>45612</v>
       </c>
       <c r="C119">
-        <v>58541</v>
+        <v>58551</v>
       </c>
       <c r="D119">
-        <v>76435</v>
+        <v>76448</v>
       </c>
       <c r="E119">
         <v>87753</v>
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="C120">
-        <v>49898</v>
+        <v>50169</v>
       </c>
       <c r="D120">
-        <v>64693</v>
+        <v>65744</v>
       </c>
       <c r="E120">
-        <v>77799</v>
+        <v>78246</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="C121">
-        <v>49898</v>
+        <v>50169</v>
       </c>
       <c r="D121">
-        <v>64693</v>
+        <v>65744</v>
       </c>
       <c r="E121">
-        <v>77799</v>
+        <v>78246</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>43017</v>
       </c>
       <c r="C122">
-        <v>52935</v>
+        <v>53067</v>
       </c>
       <c r="D122">
-        <v>69525</v>
+        <v>69802</v>
       </c>
       <c r="E122">
-        <v>81398</v>
+        <v>81556</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>42907</v>
       </c>
       <c r="C123">
-        <v>52652</v>
+        <v>52794</v>
       </c>
       <c r="D123">
-        <v>68925</v>
+        <v>69279</v>
       </c>
       <c r="E123">
-        <v>80705</v>
+        <v>81003</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>43017</v>
       </c>
       <c r="C124">
-        <v>52935</v>
+        <v>53067</v>
       </c>
       <c r="D124">
-        <v>69525</v>
+        <v>69802</v>
       </c>
       <c r="E124">
-        <v>81398</v>
+        <v>81556</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2476,16 +2476,16 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>42248</v>
+        <v>42251</v>
       </c>
       <c r="C125">
-        <v>52101</v>
+        <v>52235</v>
       </c>
       <c r="D125">
-        <v>68677</v>
+        <v>68956</v>
       </c>
       <c r="E125">
-        <v>80567</v>
+        <v>80732</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2493,16 +2493,16 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>46607</v>
+        <v>46609</v>
       </c>
       <c r="C126">
-        <v>57528</v>
+        <v>57594</v>
       </c>
       <c r="D126">
-        <v>74477</v>
+        <v>74573</v>
       </c>
       <c r="E126">
-        <v>85042</v>
+        <v>85087</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>49085</v>
+        <v>49095</v>
       </c>
       <c r="C127">
-        <v>59915</v>
+        <v>60029</v>
       </c>
       <c r="D127">
-        <v>76257</v>
+        <v>76365</v>
       </c>
       <c r="E127">
-        <v>86372</v>
+        <v>86424</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,10 +2530,10 @@
         <v>52662</v>
       </c>
       <c r="C128">
-        <v>63936</v>
+        <v>63950</v>
       </c>
       <c r="D128">
-        <v>79124</v>
+        <v>79136</v>
       </c>
       <c r="E128">
         <v>89384</v>
@@ -2547,10 +2547,10 @@
         <v>52662</v>
       </c>
       <c r="C129">
-        <v>63936</v>
+        <v>63950</v>
       </c>
       <c r="D129">
-        <v>79124</v>
+        <v>79136</v>
       </c>
       <c r="E129">
         <v>89384</v>
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>45897</v>
+        <v>45899</v>
       </c>
       <c r="C130">
-        <v>52084</v>
+        <v>52225</v>
       </c>
       <c r="D130">
-        <v>65356</v>
+        <v>66143</v>
       </c>
       <c r="E130">
-        <v>77356</v>
+        <v>77887</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="C131">
-        <v>50754</v>
+        <v>50959</v>
       </c>
       <c r="D131">
-        <v>61767</v>
+        <v>63381</v>
       </c>
       <c r="E131">
-        <v>71204</v>
+        <v>73609</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>45671</v>
+        <v>45674</v>
       </c>
       <c r="C132">
-        <v>50854</v>
+        <v>51053</v>
       </c>
       <c r="D132">
-        <v>62034</v>
+        <v>63587</v>
       </c>
       <c r="E132">
-        <v>71662</v>
+        <v>73928</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>45757</v>
+        <v>45761</v>
       </c>
       <c r="C133">
-        <v>51326</v>
+        <v>51503</v>
       </c>
       <c r="D133">
-        <v>63310</v>
+        <v>64568</v>
       </c>
       <c r="E133">
-        <v>73848</v>
+        <v>75448</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2629,16 +2629,16 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>44708</v>
+        <v>44715</v>
       </c>
       <c r="C134">
-        <v>50143</v>
+        <v>50383</v>
       </c>
       <c r="D134">
-        <v>61410</v>
+        <v>63413</v>
       </c>
       <c r="E134">
-        <v>71148</v>
+        <v>73758</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2646,16 +2646,16 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="C135">
-        <v>51926</v>
+        <v>52049</v>
       </c>
       <c r="D135">
-        <v>65020</v>
+        <v>65791</v>
       </c>
       <c r="E135">
-        <v>76953</v>
+        <v>77512</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2666,13 +2666,13 @@
         <v>45348</v>
       </c>
       <c r="C136">
-        <v>51011</v>
+        <v>51143</v>
       </c>
       <c r="D136">
-        <v>63757</v>
+        <v>64588</v>
       </c>
       <c r="E136">
-        <v>75484</v>
+        <v>76191</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2683,13 +2683,13 @@
         <v>45382</v>
       </c>
       <c r="C137">
-        <v>51220</v>
+        <v>51343</v>
       </c>
       <c r="D137">
-        <v>64374</v>
+        <v>65063</v>
       </c>
       <c r="E137">
-        <v>76584</v>
+        <v>76953</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2700,13 +2700,13 @@
         <v>45382</v>
       </c>
       <c r="C138">
-        <v>51220</v>
+        <v>51343</v>
       </c>
       <c r="D138">
-        <v>64374</v>
+        <v>65063</v>
       </c>
       <c r="E138">
-        <v>76584</v>
+        <v>76953</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>44707</v>
       </c>
       <c r="C139">
-        <v>50908</v>
+        <v>51085</v>
       </c>
       <c r="D139">
-        <v>64504</v>
+        <v>65286</v>
       </c>
       <c r="E139">
-        <v>76955</v>
+        <v>77345</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2734,10 +2734,10 @@
         <v>47654</v>
       </c>
       <c r="C140">
-        <v>55086</v>
+        <v>55136</v>
       </c>
       <c r="D140">
-        <v>62401</v>
+        <v>62499</v>
       </c>
       <c r="E140">
         <v>74041</v>
@@ -2751,13 +2751,13 @@
         <v>44707</v>
       </c>
       <c r="C141">
-        <v>50908</v>
+        <v>51085</v>
       </c>
       <c r="D141">
-        <v>64504</v>
+        <v>65286</v>
       </c>
       <c r="E141">
-        <v>76955</v>
+        <v>77345</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>44688</v>
       </c>
       <c r="C142">
-        <v>50800</v>
+        <v>50984</v>
       </c>
       <c r="D142">
-        <v>64202</v>
+        <v>65057</v>
       </c>
       <c r="E142">
-        <v>76443</v>
+        <v>76993</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>44356</v>
       </c>
       <c r="C143">
-        <v>51678</v>
+        <v>51882</v>
       </c>
       <c r="D143">
-        <v>63574</v>
+        <v>64550</v>
       </c>
       <c r="E143">
-        <v>73825</v>
+        <v>75369</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>45319</v>
       </c>
       <c r="C144">
-        <v>54335</v>
+        <v>54443</v>
       </c>
       <c r="D144">
-        <v>69625</v>
+        <v>69859</v>
       </c>
       <c r="E144">
-        <v>81005</v>
+        <v>81144</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>45319</v>
       </c>
       <c r="C145">
-        <v>54335</v>
+        <v>54443</v>
       </c>
       <c r="D145">
-        <v>69625</v>
+        <v>69859</v>
       </c>
       <c r="E145">
-        <v>81005</v>
+        <v>81144</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,10 +2836,10 @@
         <v>52132</v>
       </c>
       <c r="C146">
-        <v>62902</v>
+        <v>62921</v>
       </c>
       <c r="D146">
-        <v>76884</v>
+        <v>76910</v>
       </c>
       <c r="E146">
         <v>87243</v>
@@ -2853,13 +2853,13 @@
         <v>47834</v>
       </c>
       <c r="C147">
-        <v>56566</v>
+        <v>56596</v>
       </c>
       <c r="D147">
-        <v>72376</v>
+        <v>72441</v>
       </c>
       <c r="E147">
-        <v>83357</v>
+        <v>83392</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>44941</v>
       </c>
       <c r="C148">
-        <v>52597</v>
+        <v>52643</v>
       </c>
       <c r="D148">
-        <v>67314</v>
+        <v>67490</v>
       </c>
       <c r="E148">
-        <v>78979</v>
+        <v>79103</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>42313</v>
       </c>
       <c r="C149">
-        <v>47684</v>
+        <v>47738</v>
       </c>
       <c r="D149">
-        <v>60582</v>
+        <v>61273</v>
       </c>
       <c r="E149">
-        <v>72991</v>
+        <v>73372</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>42313</v>
       </c>
       <c r="C150">
-        <v>47684</v>
+        <v>47738</v>
       </c>
       <c r="D150">
-        <v>60582</v>
+        <v>61273</v>
       </c>
       <c r="E150">
-        <v>72991</v>
+        <v>73372</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>42278</v>
       </c>
       <c r="C151">
-        <v>47388</v>
+        <v>47449</v>
       </c>
       <c r="D151">
-        <v>59594</v>
+        <v>60514</v>
       </c>
       <c r="E151">
-        <v>71181</v>
+        <v>72122</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>42313</v>
       </c>
       <c r="C152">
-        <v>47684</v>
+        <v>47738</v>
       </c>
       <c r="D152">
-        <v>60582</v>
+        <v>61273</v>
       </c>
       <c r="E152">
-        <v>72991</v>
+        <v>73372</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,10 +2955,10 @@
         <v>46718</v>
       </c>
       <c r="C153">
-        <v>57040</v>
+        <v>57071</v>
       </c>
       <c r="D153">
-        <v>73538</v>
+        <v>73552</v>
       </c>
       <c r="E153">
         <v>85479</v>
@@ -2972,10 +2972,10 @@
         <v>46718</v>
       </c>
       <c r="C154">
-        <v>57040</v>
+        <v>57071</v>
       </c>
       <c r="D154">
-        <v>73538</v>
+        <v>73552</v>
       </c>
       <c r="E154">
         <v>85479</v>
@@ -2989,13 +2989,13 @@
         <v>39919</v>
       </c>
       <c r="C155">
-        <v>47206</v>
+        <v>47284</v>
       </c>
       <c r="D155">
-        <v>62089</v>
+        <v>62306</v>
       </c>
       <c r="E155">
-        <v>74322</v>
+        <v>74451</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>39919</v>
       </c>
       <c r="C156">
-        <v>47206</v>
+        <v>47284</v>
       </c>
       <c r="D156">
-        <v>62089</v>
+        <v>62306</v>
       </c>
       <c r="E156">
-        <v>74322</v>
+        <v>74451</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>42804</v>
       </c>
       <c r="C157">
-        <v>51068</v>
+        <v>51116</v>
       </c>
       <c r="D157">
-        <v>67269</v>
+        <v>67347</v>
       </c>
       <c r="E157">
-        <v>79129</v>
+        <v>79165</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>41512</v>
       </c>
       <c r="C158">
-        <v>49223</v>
+        <v>49279</v>
       </c>
       <c r="D158">
-        <v>64397</v>
+        <v>64603</v>
       </c>
       <c r="E158">
-        <v>76499</v>
+        <v>76635</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>40256</v>
       </c>
       <c r="C159">
-        <v>45443</v>
+        <v>45544</v>
       </c>
       <c r="D159">
-        <v>58417</v>
+        <v>59152</v>
       </c>
       <c r="E159">
-        <v>71008</v>
+        <v>71405</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>39104</v>
       </c>
       <c r="C160">
-        <v>46752</v>
+        <v>46799</v>
       </c>
       <c r="D160">
-        <v>62200</v>
+        <v>62424</v>
       </c>
       <c r="E160">
-        <v>74672</v>
+        <v>74817</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3091,13 +3091,13 @@
         <v>41675</v>
       </c>
       <c r="C161">
-        <v>51070</v>
+        <v>51151</v>
       </c>
       <c r="D161">
-        <v>68345</v>
+        <v>68427</v>
       </c>
       <c r="E161">
-        <v>80354</v>
+        <v>80397</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,10 +3108,10 @@
         <v>45145</v>
       </c>
       <c r="C162">
-        <v>55659</v>
+        <v>55670</v>
       </c>
       <c r="D162">
-        <v>72457</v>
+        <v>72473</v>
       </c>
       <c r="E162">
         <v>84696</v>
@@ -3125,13 +3125,13 @@
         <v>40877</v>
       </c>
       <c r="C163">
-        <v>46461</v>
+        <v>46523</v>
       </c>
       <c r="D163">
-        <v>59684</v>
+        <v>60448</v>
       </c>
       <c r="E163">
-        <v>72420</v>
+        <v>72809</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>42289</v>
       </c>
       <c r="C164">
-        <v>50325</v>
+        <v>50360</v>
       </c>
       <c r="D164">
-        <v>65680</v>
+        <v>65889</v>
       </c>
       <c r="E164">
-        <v>77757</v>
+        <v>77890</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>39412</v>
       </c>
       <c r="C165">
-        <v>47354</v>
+        <v>47369</v>
       </c>
       <c r="D165">
-        <v>62922</v>
+        <v>63143</v>
       </c>
       <c r="E165">
-        <v>75292</v>
+        <v>75435</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>39412</v>
       </c>
       <c r="C166">
-        <v>47354</v>
+        <v>47369</v>
       </c>
       <c r="D166">
-        <v>62922</v>
+        <v>63143</v>
       </c>
       <c r="E166">
-        <v>75292</v>
+        <v>75435</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>42019</v>
       </c>
       <c r="C167">
-        <v>51970</v>
+        <v>52111</v>
       </c>
       <c r="D167">
-        <v>69589</v>
+        <v>69677</v>
       </c>
       <c r="E167">
-        <v>81514</v>
+        <v>81557</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>47223</v>
       </c>
       <c r="C168">
-        <v>58821</v>
+        <v>58844</v>
       </c>
       <c r="D168">
-        <v>76327</v>
+        <v>76338</v>
       </c>
       <c r="E168">
-        <v>87229</v>
+        <v>87237</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3224,16 +3224,16 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>45275</v>
+        <v>45276</v>
       </c>
       <c r="C169">
-        <v>52023</v>
+        <v>52235</v>
       </c>
       <c r="D169">
-        <v>65856</v>
+        <v>66752</v>
       </c>
       <c r="E169">
-        <v>78133</v>
+        <v>78643</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>45519</v>
       </c>
       <c r="C170">
-        <v>51040</v>
+        <v>51094</v>
       </c>
       <c r="D170">
-        <v>63467</v>
+        <v>64338</v>
       </c>
       <c r="E170">
-        <v>74672</v>
+        <v>75808</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3258,16 +3258,16 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>45294</v>
+        <v>45296</v>
       </c>
       <c r="C171">
-        <v>52109</v>
+        <v>52317</v>
       </c>
       <c r="D171">
-        <v>66069</v>
+        <v>66912</v>
       </c>
       <c r="E171">
-        <v>78479</v>
+        <v>78879</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>45585</v>
       </c>
       <c r="C172">
-        <v>51514</v>
+        <v>51559</v>
       </c>
       <c r="D172">
-        <v>64913</v>
+        <v>65499</v>
       </c>
       <c r="E172">
-        <v>77259</v>
+        <v>77619</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>45465</v>
       </c>
       <c r="C173">
-        <v>50652</v>
+        <v>50713</v>
       </c>
       <c r="D173">
-        <v>62284</v>
+        <v>63389</v>
       </c>
       <c r="E173">
-        <v>72556</v>
+        <v>74326</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3309,16 +3309,16 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="C174">
-        <v>50810</v>
+        <v>50899</v>
       </c>
       <c r="D174">
-        <v>61688</v>
+        <v>62944</v>
       </c>
       <c r="E174">
-        <v>70999</v>
+        <v>73171</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>49255</v>
+        <v>49256</v>
       </c>
       <c r="C175">
-        <v>59156</v>
+        <v>59195</v>
       </c>
       <c r="D175">
-        <v>75477</v>
+        <v>75546</v>
       </c>
       <c r="E175">
-        <v>86059</v>
+        <v>86096</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="C176">
-        <v>54780</v>
+        <v>54848</v>
       </c>
       <c r="D176">
-        <v>70430</v>
+        <v>70621</v>
       </c>
       <c r="E176">
-        <v>82086</v>
+        <v>82219</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="C177">
-        <v>54780</v>
+        <v>54848</v>
       </c>
       <c r="D177">
-        <v>70430</v>
+        <v>70621</v>
       </c>
       <c r="E177">
-        <v>82086</v>
+        <v>82219</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3380,13 +3380,13 @@
         <v>45423</v>
       </c>
       <c r="C178">
-        <v>51409</v>
+        <v>51480</v>
       </c>
       <c r="D178">
-        <v>64816</v>
+        <v>65457</v>
       </c>
       <c r="E178">
-        <v>77092</v>
+        <v>77465</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3397,13 +3397,13 @@
         <v>46079</v>
       </c>
       <c r="C179">
-        <v>54436</v>
+        <v>54484</v>
       </c>
       <c r="D179">
-        <v>69606</v>
+        <v>69773</v>
       </c>
       <c r="E179">
-        <v>81122</v>
+        <v>81253</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3414,13 +3414,13 @@
         <v>53711</v>
       </c>
       <c r="C180">
-        <v>64872</v>
+        <v>64875</v>
       </c>
       <c r="D180">
-        <v>80720</v>
+        <v>80728</v>
       </c>
       <c r="E180">
-        <v>90059</v>
+        <v>90065</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3431,13 +3431,13 @@
         <v>53711</v>
       </c>
       <c r="C181">
-        <v>64872</v>
+        <v>64875</v>
       </c>
       <c r="D181">
-        <v>80720</v>
+        <v>80728</v>
       </c>
       <c r="E181">
-        <v>90059</v>
+        <v>90065</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3448,13 +3448,13 @@
         <v>48064</v>
       </c>
       <c r="C182">
-        <v>58526</v>
+        <v>58532</v>
       </c>
       <c r="D182">
-        <v>75584</v>
+        <v>75596</v>
       </c>
       <c r="E182">
-        <v>86493</v>
+        <v>86500</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3468,10 +3468,10 @@
         <v>54838</v>
       </c>
       <c r="D183">
-        <v>72308</v>
+        <v>72318</v>
       </c>
       <c r="E183">
-        <v>84296</v>
+        <v>84303</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>46779</v>
       </c>
       <c r="C184">
-        <v>56418</v>
+        <v>56445</v>
       </c>
       <c r="D184">
-        <v>73088</v>
+        <v>73164</v>
       </c>
       <c r="E184">
-        <v>84175</v>
+        <v>84215</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>46779</v>
       </c>
       <c r="C185">
-        <v>56418</v>
+        <v>56445</v>
       </c>
       <c r="D185">
-        <v>73088</v>
+        <v>73164</v>
       </c>
       <c r="E185">
-        <v>84175</v>
+        <v>84215</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,10 +3516,10 @@
         <v>47217</v>
       </c>
       <c r="C186">
-        <v>58149</v>
+        <v>58155</v>
       </c>
       <c r="D186">
-        <v>74919</v>
+        <v>74936</v>
       </c>
       <c r="E186">
         <v>86571</v>
@@ -3533,13 +3533,13 @@
         <v>44182</v>
       </c>
       <c r="C187">
-        <v>53349</v>
+        <v>53372</v>
       </c>
       <c r="D187">
-        <v>70138</v>
+        <v>70227</v>
       </c>
       <c r="E187">
-        <v>81737</v>
+        <v>81778</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3550,10 +3550,10 @@
         <v>46117</v>
       </c>
       <c r="C188">
-        <v>56733</v>
+        <v>56755</v>
       </c>
       <c r="D188">
-        <v>73758</v>
+        <v>73775</v>
       </c>
       <c r="E188">
         <v>85842</v>
@@ -3567,13 +3567,13 @@
         <v>47704</v>
       </c>
       <c r="C189">
-        <v>58276</v>
+        <v>58290</v>
       </c>
       <c r="D189">
-        <v>75610</v>
+        <v>75622</v>
       </c>
       <c r="E189">
-        <v>86603</v>
+        <v>86611</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3584,13 +3584,13 @@
         <v>47704</v>
       </c>
       <c r="C190">
-        <v>58276</v>
+        <v>58290</v>
       </c>
       <c r="D190">
-        <v>75610</v>
+        <v>75622</v>
       </c>
       <c r="E190">
-        <v>86603</v>
+        <v>86611</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3601,13 +3601,13 @@
         <v>47000</v>
       </c>
       <c r="C191">
-        <v>56711</v>
+        <v>56758</v>
       </c>
       <c r="D191">
-        <v>73303</v>
+        <v>73385</v>
       </c>
       <c r="E191">
-        <v>84296</v>
+        <v>84336</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>44182</v>
       </c>
       <c r="C192">
-        <v>53349</v>
+        <v>53372</v>
       </c>
       <c r="D192">
-        <v>70138</v>
+        <v>70227</v>
       </c>
       <c r="E192">
-        <v>81737</v>
+        <v>81778</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>43773</v>
       </c>
       <c r="C193">
-        <v>50203</v>
+        <v>50344</v>
       </c>
       <c r="D193">
-        <v>64141</v>
+        <v>64891</v>
       </c>
       <c r="E193">
-        <v>76865</v>
+        <v>77256</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>43551</v>
       </c>
       <c r="C194">
-        <v>49066</v>
+        <v>49261</v>
       </c>
       <c r="D194">
-        <v>61007</v>
+        <v>62467</v>
       </c>
       <c r="E194">
-        <v>71554</v>
+        <v>73578</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3666,16 +3666,16 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="C195">
-        <v>51893</v>
+        <v>52114</v>
       </c>
       <c r="D195">
-        <v>65537</v>
+        <v>66512</v>
       </c>
       <c r="E195">
-        <v>77613</v>
+        <v>78289</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>43044</v>
       </c>
       <c r="C196">
-        <v>49426</v>
+        <v>49565</v>
       </c>
       <c r="D196">
-        <v>63575</v>
+        <v>64326</v>
       </c>
       <c r="E196">
-        <v>76511</v>
+        <v>76915</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>42194</v>
       </c>
       <c r="C197">
-        <v>48630</v>
+        <v>48725</v>
       </c>
       <c r="D197">
-        <v>62922</v>
+        <v>63673</v>
       </c>
       <c r="E197">
-        <v>76036</v>
+        <v>76462</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>42091</v>
       </c>
       <c r="C198">
-        <v>48043</v>
+        <v>48157</v>
       </c>
       <c r="D198">
-        <v>61229</v>
+        <v>62345</v>
       </c>
       <c r="E198">
-        <v>73171</v>
+        <v>74509</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>43569</v>
       </c>
       <c r="C199">
-        <v>52417</v>
+        <v>52479</v>
       </c>
       <c r="D199">
-        <v>68029</v>
+        <v>68360</v>
       </c>
       <c r="E199">
-        <v>79728</v>
+        <v>80182</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>43745</v>
       </c>
       <c r="C200">
-        <v>52944</v>
+        <v>52996</v>
       </c>
       <c r="D200">
-        <v>69319</v>
+        <v>69520</v>
       </c>
       <c r="E200">
-        <v>81284</v>
+        <v>81432</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>45844</v>
       </c>
       <c r="C201">
-        <v>56078</v>
+        <v>56140</v>
       </c>
       <c r="D201">
-        <v>72070</v>
+        <v>72345</v>
       </c>
       <c r="E201">
-        <v>82110</v>
+        <v>82360</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,10 +3788,10 @@
         <v>47278</v>
       </c>
       <c r="C202">
-        <v>58545</v>
+        <v>58557</v>
       </c>
       <c r="D202">
-        <v>71938</v>
+        <v>71991</v>
       </c>
       <c r="E202">
         <v>82481</v>
@@ -3805,13 +3805,13 @@
         <v>44557</v>
       </c>
       <c r="C203">
-        <v>53579</v>
+        <v>53655</v>
       </c>
       <c r="D203">
-        <v>69660</v>
+        <v>69860</v>
       </c>
       <c r="E203">
-        <v>81516</v>
+        <v>81655</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3819,16 +3819,16 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>42487</v>
+        <v>42490</v>
       </c>
       <c r="C204">
-        <v>51920</v>
+        <v>52028</v>
       </c>
       <c r="D204">
-        <v>68720</v>
+        <v>68951</v>
       </c>
       <c r="E204">
-        <v>80901</v>
+        <v>81058</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3836,16 +3836,16 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C205">
-        <v>56928</v>
+        <v>56980</v>
       </c>
       <c r="D205">
-        <v>74277</v>
+        <v>74361</v>
       </c>
       <c r="E205">
-        <v>85167</v>
+        <v>85211</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3853,16 +3853,16 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>20882</v>
+        <v>20891</v>
       </c>
       <c r="C206">
-        <v>26427</v>
+        <v>26685</v>
       </c>
       <c r="D206">
-        <v>44038</v>
+        <v>45329</v>
       </c>
       <c r="E206">
-        <v>62075</v>
+        <v>62866</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="C207">
-        <v>24398</v>
+        <v>24529</v>
       </c>
       <c r="D207">
-        <v>40675</v>
+        <v>41654</v>
       </c>
       <c r="E207">
-        <v>58138</v>
+        <v>58853</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="C208">
-        <v>24398</v>
+        <v>24529</v>
       </c>
       <c r="D208">
-        <v>40675</v>
+        <v>41654</v>
       </c>
       <c r="E208">
-        <v>58138</v>
+        <v>58853</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3904,16 +3904,16 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>20619</v>
+        <v>20629</v>
       </c>
       <c r="C209">
-        <v>25086</v>
+        <v>25411</v>
       </c>
       <c r="D209">
-        <v>39833</v>
+        <v>41954</v>
       </c>
       <c r="E209">
-        <v>55353</v>
+        <v>58388</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="C210">
-        <v>24398</v>
+        <v>24529</v>
       </c>
       <c r="D210">
-        <v>40675</v>
+        <v>41654</v>
       </c>
       <c r="E210">
-        <v>58138</v>
+        <v>58853</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>22050</v>
       </c>
       <c r="C211">
-        <v>29566</v>
+        <v>29626</v>
       </c>
       <c r="D211">
-        <v>50268</v>
+        <v>50506</v>
       </c>
       <c r="E211">
-        <v>66560</v>
+        <v>66817</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>24509</v>
+        <v>24511</v>
       </c>
       <c r="C212">
-        <v>34049</v>
+        <v>34175</v>
       </c>
       <c r="D212">
-        <v>55315</v>
+        <v>55674</v>
       </c>
       <c r="E212">
-        <v>70715</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>19959</v>
+        <v>19960</v>
       </c>
       <c r="C213">
-        <v>24398</v>
+        <v>24529</v>
       </c>
       <c r="D213">
-        <v>40675</v>
+        <v>41654</v>
       </c>
       <c r="E213">
-        <v>58138</v>
+        <v>58853</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>20258</v>
       </c>
       <c r="C214">
-        <v>26211</v>
+        <v>26231</v>
       </c>
       <c r="D214">
-        <v>45441</v>
+        <v>45600</v>
       </c>
       <c r="E214">
-        <v>61441</v>
+        <v>61660</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>20258</v>
       </c>
       <c r="C215">
-        <v>26211</v>
+        <v>26231</v>
       </c>
       <c r="D215">
-        <v>45441</v>
+        <v>45600</v>
       </c>
       <c r="E215">
-        <v>61441</v>
+        <v>61660</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>19804</v>
       </c>
       <c r="C216">
-        <v>25347</v>
+        <v>25362</v>
       </c>
       <c r="D216">
-        <v>44208</v>
+        <v>44351</v>
       </c>
       <c r="E216">
-        <v>60240</v>
+        <v>60444</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>20189</v>
       </c>
       <c r="C217">
-        <v>26709</v>
+        <v>26739</v>
       </c>
       <c r="D217">
-        <v>46539</v>
+        <v>46723</v>
       </c>
       <c r="E217">
-        <v>62661</v>
+        <v>62896</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>22951</v>
       </c>
       <c r="C218">
-        <v>32304</v>
+        <v>32320</v>
       </c>
       <c r="D218">
-        <v>54807</v>
+        <v>54884</v>
       </c>
       <c r="E218">
-        <v>70112</v>
+        <v>70187</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>24675</v>
       </c>
       <c r="C219">
-        <v>33436</v>
+        <v>33495</v>
       </c>
       <c r="D219">
-        <v>54307</v>
+        <v>54598</v>
       </c>
       <c r="E219">
-        <v>69787</v>
+        <v>70060</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>25217</v>
+        <v>25225</v>
       </c>
       <c r="C220">
-        <v>35544</v>
+        <v>35721</v>
       </c>
       <c r="D220">
-        <v>57036</v>
+        <v>57449</v>
       </c>
       <c r="E220">
-        <v>72188</v>
+        <v>72479</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>29965</v>
       </c>
       <c r="C221">
-        <v>41673</v>
+        <v>41704</v>
       </c>
       <c r="D221">
-        <v>63548</v>
+        <v>63665</v>
       </c>
       <c r="E221">
-        <v>77082</v>
+        <v>77161</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>24675</v>
       </c>
       <c r="C222">
-        <v>33436</v>
+        <v>33495</v>
       </c>
       <c r="D222">
-        <v>54307</v>
+        <v>54598</v>
       </c>
       <c r="E222">
-        <v>69787</v>
+        <v>70060</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>37166</v>
       </c>
       <c r="C223">
-        <v>52054</v>
+        <v>52060</v>
       </c>
       <c r="D223">
-        <v>73195</v>
+        <v>73214</v>
       </c>
       <c r="E223">
-        <v>84618</v>
+        <v>84638</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4162,10 +4162,10 @@
         <v>23329</v>
       </c>
       <c r="C224">
-        <v>33624</v>
+        <v>33625</v>
       </c>
       <c r="D224">
-        <v>57573</v>
+        <v>57582</v>
       </c>
       <c r="E224">
         <v>74668</v>
@@ -4179,13 +4179,13 @@
         <v>18952</v>
       </c>
       <c r="C225">
-        <v>23548</v>
+        <v>23556</v>
       </c>
       <c r="D225">
-        <v>41836</v>
+        <v>41936</v>
       </c>
       <c r="E225">
-        <v>58304</v>
+        <v>58480</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4196,13 +4196,13 @@
         <v>20855</v>
       </c>
       <c r="C226">
-        <v>27840</v>
+        <v>27845</v>
       </c>
       <c r="D226">
-        <v>49568</v>
+        <v>49609</v>
       </c>
       <c r="E226">
-        <v>66249</v>
+        <v>66308</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>18936</v>
       </c>
       <c r="C227">
-        <v>22767</v>
+        <v>22789</v>
       </c>
       <c r="D227">
-        <v>37360</v>
+        <v>37699</v>
       </c>
       <c r="E227">
-        <v>50830</v>
+        <v>52092</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,10 +4230,10 @@
         <v>21591</v>
       </c>
       <c r="C228">
-        <v>30818</v>
+        <v>30819</v>
       </c>
       <c r="D228">
-        <v>55790</v>
+        <v>55796</v>
       </c>
       <c r="E228">
         <v>74504</v>
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>25217</v>
+        <v>25225</v>
       </c>
       <c r="C229">
-        <v>35544</v>
+        <v>35721</v>
       </c>
       <c r="D229">
-        <v>57036</v>
+        <v>57449</v>
       </c>
       <c r="E229">
-        <v>72188</v>
+        <v>72479</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>25890</v>
       </c>
       <c r="C230">
-        <v>34816</v>
+        <v>34871</v>
       </c>
       <c r="D230">
-        <v>55307</v>
+        <v>55604</v>
       </c>
       <c r="E230">
-        <v>70495</v>
+        <v>70755</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>28875</v>
+        <v>28877</v>
       </c>
       <c r="C231">
-        <v>41121</v>
+        <v>41184</v>
       </c>
       <c r="D231">
-        <v>63440</v>
+        <v>63589</v>
       </c>
       <c r="E231">
-        <v>77036</v>
+        <v>77121</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>25730</v>
       </c>
       <c r="C232">
-        <v>36518</v>
+        <v>36542</v>
       </c>
       <c r="D232">
-        <v>59097</v>
+        <v>59200</v>
       </c>
       <c r="E232">
-        <v>73664</v>
+        <v>73747</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4315,13 +4315,13 @@
         <v>31900</v>
       </c>
       <c r="C233">
-        <v>46376</v>
+        <v>46381</v>
       </c>
       <c r="D233">
-        <v>69075</v>
+        <v>69099</v>
       </c>
       <c r="E233">
-        <v>81706</v>
+        <v>81730</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,10 +4332,10 @@
         <v>33649</v>
       </c>
       <c r="C234">
-        <v>48176</v>
+        <v>48188</v>
       </c>
       <c r="D234">
-        <v>69495</v>
+        <v>69519</v>
       </c>
       <c r="E234">
         <v>82455</v>
@@ -4349,10 +4349,10 @@
         <v>33649</v>
       </c>
       <c r="C235">
-        <v>48176</v>
+        <v>48188</v>
       </c>
       <c r="D235">
-        <v>69495</v>
+        <v>69519</v>
       </c>
       <c r="E235">
         <v>82455</v>
@@ -4366,13 +4366,13 @@
         <v>35816</v>
       </c>
       <c r="C236">
-        <v>50501</v>
+        <v>50508</v>
       </c>
       <c r="D236">
-        <v>71750</v>
+        <v>71767</v>
       </c>
       <c r="E236">
-        <v>83423</v>
+        <v>83444</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>21185</v>
       </c>
       <c r="C237">
-        <v>28245</v>
+        <v>28252</v>
       </c>
       <c r="D237">
-        <v>49533</v>
+        <v>49582</v>
       </c>
       <c r="E237">
-        <v>65757</v>
+        <v>65816</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>19184</v>
       </c>
       <c r="C238">
-        <v>23961</v>
+        <v>23976</v>
       </c>
       <c r="D238">
-        <v>41993</v>
+        <v>42109</v>
       </c>
       <c r="E238">
-        <v>58035</v>
+        <v>58212</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4417,13 +4417,13 @@
         <v>24775</v>
       </c>
       <c r="C239">
-        <v>35471</v>
+        <v>35472</v>
       </c>
       <c r="D239">
-        <v>59340</v>
+        <v>59349</v>
       </c>
       <c r="E239">
-        <v>74931</v>
+        <v>74950</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,10 +4434,10 @@
         <v>23221</v>
       </c>
       <c r="C240">
-        <v>32687</v>
+        <v>32688</v>
       </c>
       <c r="D240">
-        <v>55254</v>
+        <v>55264</v>
       </c>
       <c r="E240">
         <v>71789</v>
@@ -4451,13 +4451,13 @@
         <v>24062</v>
       </c>
       <c r="C241">
-        <v>34524</v>
+        <v>34525</v>
       </c>
       <c r="D241">
-        <v>58387</v>
+        <v>58395</v>
       </c>
       <c r="E241">
-        <v>73812</v>
+        <v>73830</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>29965</v>
       </c>
       <c r="C242">
-        <v>41673</v>
+        <v>41704</v>
       </c>
       <c r="D242">
-        <v>63548</v>
+        <v>63665</v>
       </c>
       <c r="E242">
-        <v>77082</v>
+        <v>77161</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>33469</v>
       </c>
       <c r="C243">
-        <v>45633</v>
+        <v>45715</v>
       </c>
       <c r="D243">
-        <v>66403</v>
+        <v>66538</v>
       </c>
       <c r="E243">
-        <v>78938</v>
+        <v>79010</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>29965</v>
       </c>
       <c r="C244">
-        <v>41673</v>
+        <v>41704</v>
       </c>
       <c r="D244">
-        <v>63548</v>
+        <v>63665</v>
       </c>
       <c r="E244">
-        <v>77082</v>
+        <v>77161</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,10 +4519,10 @@
         <v>38670</v>
       </c>
       <c r="C245">
-        <v>53375</v>
+        <v>53409</v>
       </c>
       <c r="D245">
-        <v>73161</v>
+        <v>73189</v>
       </c>
       <c r="E245">
         <v>84978</v>
@@ -4533,13 +4533,13 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>37855</v>
+        <v>37856</v>
       </c>
       <c r="C246">
-        <v>53167</v>
+        <v>53200</v>
       </c>
       <c r="D246">
-        <v>73428</v>
+        <v>73459</v>
       </c>
       <c r="E246">
         <v>85299</v>
@@ -4550,13 +4550,13 @@
         <v>246</v>
       </c>
       <c r="B247">
-        <v>37855</v>
+        <v>37856</v>
       </c>
       <c r="C247">
-        <v>53167</v>
+        <v>53200</v>
       </c>
       <c r="D247">
-        <v>73428</v>
+        <v>73459</v>
       </c>
       <c r="E247">
         <v>85299</v>
@@ -4570,10 +4570,10 @@
         <v>29477</v>
       </c>
       <c r="C248">
-        <v>43175</v>
+        <v>43184</v>
       </c>
       <c r="D248">
-        <v>66205</v>
+        <v>66227</v>
       </c>
       <c r="E248">
         <v>80745</v>
@@ -4587,13 +4587,13 @@
         <v>22526</v>
       </c>
       <c r="C249">
-        <v>32224</v>
+        <v>32225</v>
       </c>
       <c r="D249">
-        <v>57869</v>
+        <v>57874</v>
       </c>
       <c r="E249">
-        <v>75543</v>
+        <v>75558</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>42151</v>
       </c>
       <c r="C250">
-        <v>52973</v>
+        <v>52991</v>
       </c>
       <c r="D250">
-        <v>70712</v>
+        <v>70830</v>
       </c>
       <c r="E250">
-        <v>81945</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4618,16 +4618,16 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="C251">
-        <v>56517</v>
+        <v>56640</v>
       </c>
       <c r="D251">
-        <v>73908</v>
+        <v>74029</v>
       </c>
       <c r="E251">
-        <v>84419</v>
+        <v>84470</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4638,13 +4638,13 @@
         <v>39003</v>
       </c>
       <c r="C252">
-        <v>50235</v>
+        <v>50251</v>
       </c>
       <c r="D252">
-        <v>69028</v>
+        <v>69152</v>
       </c>
       <c r="E252">
-        <v>80790</v>
+        <v>80850</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>47042</v>
       </c>
       <c r="C253">
-        <v>60032</v>
+        <v>60037</v>
       </c>
       <c r="D253">
-        <v>77851</v>
+        <v>77866</v>
       </c>
       <c r="E253">
-        <v>87865</v>
+        <v>87873</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>51351</v>
       </c>
       <c r="C254">
-        <v>63596</v>
+        <v>63614</v>
       </c>
       <c r="D254">
-        <v>80207</v>
+        <v>80218</v>
       </c>
       <c r="E254">
-        <v>89566</v>
+        <v>89573</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>47042</v>
       </c>
       <c r="C255">
-        <v>60032</v>
+        <v>60037</v>
       </c>
       <c r="D255">
-        <v>77851</v>
+        <v>77866</v>
       </c>
       <c r="E255">
-        <v>87865</v>
+        <v>87873</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4706,13 +4706,13 @@
         <v>42924</v>
       </c>
       <c r="C256">
-        <v>56456</v>
+        <v>56461</v>
       </c>
       <c r="D256">
-        <v>75266</v>
+        <v>75284</v>
       </c>
       <c r="E256">
-        <v>85782</v>
+        <v>85793</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4726,10 +4726,10 @@
         <v>50736</v>
       </c>
       <c r="D257">
-        <v>71045</v>
+        <v>71061</v>
       </c>
       <c r="E257">
-        <v>82807</v>
+        <v>82820</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>50298</v>
       </c>
       <c r="D258">
-        <v>69935</v>
+        <v>69939</v>
       </c>
       <c r="E258">
-        <v>81930</v>
+        <v>81940</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>50298</v>
       </c>
       <c r="D259">
-        <v>69935</v>
+        <v>69939</v>
       </c>
       <c r="E259">
-        <v>81930</v>
+        <v>81940</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4774,13 +4774,13 @@
         <v>17197</v>
       </c>
       <c r="C260">
-        <v>26163</v>
+        <v>26164</v>
       </c>
       <c r="D260">
-        <v>49085</v>
+        <v>49147</v>
       </c>
       <c r="E260">
-        <v>65855</v>
+        <v>65925</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>23042</v>
       </c>
       <c r="D261">
-        <v>49075</v>
+        <v>49078</v>
       </c>
       <c r="E261">
-        <v>67073</v>
+        <v>67088</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4811,10 +4811,10 @@
         <v>25695</v>
       </c>
       <c r="D262">
-        <v>48354</v>
+        <v>48414</v>
       </c>
       <c r="E262">
-        <v>65012</v>
+        <v>65081</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4828,7 +4828,7 @@
         <v>31971</v>
       </c>
       <c r="D263">
-        <v>55714</v>
+        <v>55726</v>
       </c>
       <c r="E263">
         <v>72753</v>
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>17812</v>
+        <v>17813</v>
       </c>
       <c r="C264">
-        <v>29167</v>
+        <v>29168</v>
       </c>
       <c r="D264">
-        <v>53634</v>
+        <v>53639</v>
       </c>
       <c r="E264">
-        <v>70343</v>
+        <v>70362</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>17812</v>
+        <v>17813</v>
       </c>
       <c r="C265">
-        <v>29167</v>
+        <v>29168</v>
       </c>
       <c r="D265">
-        <v>53634</v>
+        <v>53639</v>
       </c>
       <c r="E265">
-        <v>70343</v>
+        <v>70362</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>27139</v>
       </c>
       <c r="C266">
-        <v>40297</v>
+        <v>40299</v>
       </c>
       <c r="D266">
-        <v>63276</v>
+        <v>63291</v>
       </c>
       <c r="E266">
-        <v>78380</v>
+        <v>78402</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>17812</v>
+        <v>17813</v>
       </c>
       <c r="C267">
-        <v>29167</v>
+        <v>29168</v>
       </c>
       <c r="D267">
-        <v>53634</v>
+        <v>53639</v>
       </c>
       <c r="E267">
-        <v>70343</v>
+        <v>70362</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>23042</v>
       </c>
       <c r="D268">
-        <v>49075</v>
+        <v>49078</v>
       </c>
       <c r="E268">
-        <v>67073</v>
+        <v>67088</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>23042</v>
       </c>
       <c r="D269">
-        <v>49075</v>
+        <v>49078</v>
       </c>
       <c r="E269">
-        <v>67073</v>
+        <v>67088</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4947,10 +4947,10 @@
         <v>28538</v>
       </c>
       <c r="D270">
-        <v>54726</v>
+        <v>54733</v>
       </c>
       <c r="E270">
-        <v>71261</v>
+        <v>71280</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4964,10 +4964,10 @@
         <v>20144</v>
       </c>
       <c r="D271">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="E271">
-        <v>63632</v>
+        <v>63642</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4981,10 +4981,10 @@
         <v>20144</v>
       </c>
       <c r="D272">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="E272">
-        <v>63632</v>
+        <v>63642</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>17664</v>
       </c>
       <c r="C273">
-        <v>32039</v>
+        <v>32040</v>
       </c>
       <c r="D273">
-        <v>57710</v>
+        <v>57723</v>
       </c>
       <c r="E273">
-        <v>73739</v>
+        <v>73761</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>17664</v>
       </c>
       <c r="C274">
-        <v>32039</v>
+        <v>32040</v>
       </c>
       <c r="D274">
-        <v>57710</v>
+        <v>57723</v>
       </c>
       <c r="E274">
-        <v>73739</v>
+        <v>73761</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5032,10 +5032,10 @@
         <v>14814</v>
       </c>
       <c r="D275">
-        <v>34770</v>
+        <v>34796</v>
       </c>
       <c r="E275">
-        <v>52812</v>
+        <v>52841</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>14477</v>
       </c>
       <c r="D276">
-        <v>36115</v>
+        <v>36116</v>
       </c>
       <c r="E276">
-        <v>55194</v>
+        <v>55199</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5066,10 +5066,10 @@
         <v>25156</v>
       </c>
       <c r="D277">
-        <v>51073</v>
+        <v>51077</v>
       </c>
       <c r="E277">
-        <v>70549</v>
+        <v>70559</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>23397</v>
       </c>
       <c r="C278">
-        <v>35458</v>
+        <v>35459</v>
       </c>
       <c r="D278">
-        <v>62482</v>
+        <v>62489</v>
       </c>
       <c r="E278">
-        <v>79503</v>
+        <v>79522</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>33021</v>
       </c>
       <c r="D279">
-        <v>58962</v>
+        <v>58966</v>
       </c>
       <c r="E279">
-        <v>76460</v>
+        <v>76472</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>33021</v>
       </c>
       <c r="D280">
-        <v>58962</v>
+        <v>58966</v>
       </c>
       <c r="E280">
-        <v>76460</v>
+        <v>76472</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5134,10 +5134,10 @@
         <v>16619</v>
       </c>
       <c r="D281">
-        <v>39953</v>
+        <v>39954</v>
       </c>
       <c r="E281">
-        <v>59947</v>
+        <v>59953</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5151,10 +5151,10 @@
         <v>14246</v>
       </c>
       <c r="D282">
-        <v>36101</v>
+        <v>36102</v>
       </c>
       <c r="E282">
-        <v>55245</v>
+        <v>55250</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5168,10 +5168,10 @@
         <v>14246</v>
       </c>
       <c r="D283">
-        <v>36101</v>
+        <v>36102</v>
       </c>
       <c r="E283">
-        <v>55245</v>
+        <v>55250</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5185,10 +5185,10 @@
         <v>14246</v>
       </c>
       <c r="D284">
-        <v>36101</v>
+        <v>36102</v>
       </c>
       <c r="E284">
-        <v>55245</v>
+        <v>55250</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>14477</v>
       </c>
       <c r="D285">
-        <v>36115</v>
+        <v>36116</v>
       </c>
       <c r="E285">
-        <v>55194</v>
+        <v>55199</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>33021</v>
       </c>
       <c r="D286">
-        <v>58962</v>
+        <v>58966</v>
       </c>
       <c r="E286">
-        <v>76460</v>
+        <v>76472</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5233,10 +5233,10 @@
         <v>36768</v>
       </c>
       <c r="C287">
-        <v>48921</v>
+        <v>48947</v>
       </c>
       <c r="D287">
-        <v>68587</v>
+        <v>68611</v>
       </c>
       <c r="E287">
         <v>82455</v>
@@ -5250,10 +5250,10 @@
         <v>30960</v>
       </c>
       <c r="C288">
-        <v>44444</v>
+        <v>44469</v>
       </c>
       <c r="D288">
-        <v>65733</v>
+        <v>65759</v>
       </c>
       <c r="E288">
         <v>80101</v>
@@ -5267,13 +5267,13 @@
         <v>43092</v>
       </c>
       <c r="C289">
-        <v>54324</v>
+        <v>54342</v>
       </c>
       <c r="D289">
-        <v>73095</v>
+        <v>73110</v>
       </c>
       <c r="E289">
-        <v>85200</v>
+        <v>85209</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5284,13 +5284,13 @@
         <v>38801</v>
       </c>
       <c r="C290">
-        <v>50846</v>
+        <v>50861</v>
       </c>
       <c r="D290">
-        <v>70612</v>
+        <v>70629</v>
       </c>
       <c r="E290">
-        <v>83386</v>
+        <v>83397</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,10 +5301,10 @@
         <v>28488</v>
       </c>
       <c r="C291">
-        <v>41941</v>
+        <v>41967</v>
       </c>
       <c r="D291">
-        <v>63621</v>
+        <v>63648</v>
       </c>
       <c r="E291">
         <v>78303</v>
@@ -5318,10 +5318,10 @@
         <v>32154</v>
       </c>
       <c r="C292">
-        <v>45667</v>
+        <v>45678</v>
       </c>
       <c r="D292">
-        <v>66200</v>
+        <v>66225</v>
       </c>
       <c r="E292">
         <v>79680</v>
@@ -5335,10 +5335,10 @@
         <v>32229</v>
       </c>
       <c r="C293">
-        <v>45755</v>
+        <v>45765</v>
       </c>
       <c r="D293">
-        <v>66349</v>
+        <v>66374</v>
       </c>
       <c r="E293">
         <v>79974</v>
@@ -5352,13 +5352,13 @@
         <v>34377</v>
       </c>
       <c r="C294">
-        <v>47913</v>
+        <v>47920</v>
       </c>
       <c r="D294">
-        <v>68395</v>
+        <v>68412</v>
       </c>
       <c r="E294">
-        <v>80695</v>
+        <v>80713</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>20709</v>
       </c>
       <c r="C295">
-        <v>28739</v>
+        <v>28759</v>
       </c>
       <c r="D295">
-        <v>48702</v>
+        <v>48937</v>
       </c>
       <c r="E295">
-        <v>64644</v>
+        <v>64859</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>22906</v>
       </c>
       <c r="C296">
-        <v>31489</v>
+        <v>31555</v>
       </c>
       <c r="D296">
-        <v>51567</v>
+        <v>51837</v>
       </c>
       <c r="E296">
-        <v>67402</v>
+        <v>67616</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>26152</v>
       </c>
       <c r="C297">
-        <v>37848</v>
+        <v>37924</v>
       </c>
       <c r="D297">
-        <v>60591</v>
+        <v>60703</v>
       </c>
       <c r="E297">
-        <v>75451</v>
+        <v>75520</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>19519</v>
       </c>
       <c r="C298">
-        <v>27990</v>
+        <v>28059</v>
       </c>
       <c r="D298">
-        <v>48535</v>
+        <v>48802</v>
       </c>
       <c r="E298">
-        <v>64867</v>
+        <v>65096</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>22394</v>
       </c>
       <c r="C299">
-        <v>33667</v>
+        <v>33722</v>
       </c>
       <c r="D299">
-        <v>56859</v>
+        <v>56959</v>
       </c>
       <c r="E299">
-        <v>72398</v>
+        <v>72471</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>20709</v>
       </c>
       <c r="C300">
-        <v>28739</v>
+        <v>28759</v>
       </c>
       <c r="D300">
-        <v>48702</v>
+        <v>48937</v>
       </c>
       <c r="E300">
-        <v>64644</v>
+        <v>64859</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>26410</v>
       </c>
       <c r="C301">
-        <v>37332</v>
+        <v>37372</v>
       </c>
       <c r="D301">
-        <v>59414</v>
+        <v>59518</v>
       </c>
       <c r="E301">
-        <v>74344</v>
+        <v>74408</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,10 +5488,10 @@
         <v>27204</v>
       </c>
       <c r="C302">
-        <v>40961</v>
+        <v>40981</v>
       </c>
       <c r="D302">
-        <v>64340</v>
+        <v>64363</v>
       </c>
       <c r="E302">
         <v>79776</v>
@@ -5505,13 +5505,13 @@
         <v>29231</v>
       </c>
       <c r="C303">
-        <v>43113</v>
+        <v>43125</v>
       </c>
       <c r="D303">
-        <v>66594</v>
+        <v>66610</v>
       </c>
       <c r="E303">
-        <v>80842</v>
+        <v>80859</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>21431</v>
       </c>
       <c r="C304">
-        <v>31394</v>
+        <v>31407</v>
       </c>
       <c r="D304">
-        <v>53792</v>
+        <v>53876</v>
       </c>
       <c r="E304">
-        <v>69522</v>
+        <v>69588</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>21431</v>
       </c>
       <c r="C305">
-        <v>31394</v>
+        <v>31407</v>
       </c>
       <c r="D305">
-        <v>53792</v>
+        <v>53876</v>
       </c>
       <c r="E305">
-        <v>69522</v>
+        <v>69588</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>21994</v>
       </c>
       <c r="C306">
-        <v>30070</v>
+        <v>30073</v>
       </c>
       <c r="D306">
-        <v>50638</v>
+        <v>50684</v>
       </c>
       <c r="E306">
-        <v>66301</v>
+        <v>66349</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>21431</v>
       </c>
       <c r="C307">
-        <v>31394</v>
+        <v>31407</v>
       </c>
       <c r="D307">
-        <v>53792</v>
+        <v>53876</v>
       </c>
       <c r="E307">
-        <v>69522</v>
+        <v>69588</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5593,7 +5593,7 @@
         <v>35751</v>
       </c>
       <c r="D308">
-        <v>58233</v>
+        <v>58245</v>
       </c>
       <c r="E308">
         <v>74591</v>
@@ -5607,13 +5607,13 @@
         <v>21994</v>
       </c>
       <c r="C309">
-        <v>30070</v>
+        <v>30073</v>
       </c>
       <c r="D309">
-        <v>50638</v>
+        <v>50684</v>
       </c>
       <c r="E309">
-        <v>66301</v>
+        <v>66349</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,10 +5624,10 @@
         <v>25111</v>
       </c>
       <c r="C310">
-        <v>38302</v>
+        <v>38309</v>
       </c>
       <c r="D310">
-        <v>61940</v>
+        <v>61959</v>
       </c>
       <c r="E310">
         <v>77608</v>
@@ -5644,10 +5644,10 @@
         <v>18958</v>
       </c>
       <c r="D311">
-        <v>43645</v>
+        <v>43647</v>
       </c>
       <c r="E311">
-        <v>62582</v>
+        <v>62594</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5661,10 +5661,10 @@
         <v>15564</v>
       </c>
       <c r="D312">
-        <v>32466</v>
+        <v>32485</v>
       </c>
       <c r="E312">
-        <v>45787</v>
+        <v>45913</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5678,10 +5678,10 @@
         <v>18958</v>
       </c>
       <c r="D313">
-        <v>43645</v>
+        <v>43647</v>
       </c>
       <c r="E313">
-        <v>62582</v>
+        <v>62594</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5695,10 +5695,10 @@
         <v>18958</v>
       </c>
       <c r="D314">
-        <v>43645</v>
+        <v>43647</v>
       </c>
       <c r="E314">
-        <v>62582</v>
+        <v>62594</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>38675</v>
       </c>
       <c r="C315">
-        <v>49317</v>
+        <v>49368</v>
       </c>
       <c r="D315">
-        <v>67901</v>
+        <v>68016</v>
       </c>
       <c r="E315">
-        <v>80120</v>
+        <v>80173</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5723,16 +5723,16 @@
         <v>315</v>
       </c>
       <c r="B316">
-        <v>40608</v>
+        <v>40611</v>
       </c>
       <c r="C316">
-        <v>49818</v>
+        <v>49942</v>
       </c>
       <c r="D316">
-        <v>66627</v>
+        <v>66899</v>
       </c>
       <c r="E316">
-        <v>79124</v>
+        <v>79286</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>41326</v>
       </c>
       <c r="C317">
-        <v>49892</v>
+        <v>49952</v>
       </c>
       <c r="D317">
-        <v>66113</v>
+        <v>66343</v>
       </c>
       <c r="E317">
-        <v>78431</v>
+        <v>78583</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>38310</v>
       </c>
       <c r="C318">
-        <v>47291</v>
+        <v>47369</v>
       </c>
       <c r="D318">
-        <v>64466</v>
+        <v>64734</v>
       </c>
       <c r="E318">
-        <v>77458</v>
+        <v>77625</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>34631</v>
       </c>
       <c r="C319">
-        <v>43206</v>
+        <v>43236</v>
       </c>
       <c r="D319">
-        <v>60441</v>
+        <v>60702</v>
       </c>
       <c r="E319">
-        <v>73683</v>
+        <v>73867</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>36152</v>
       </c>
       <c r="C320">
-        <v>45067</v>
+        <v>45180</v>
       </c>
       <c r="D320">
-        <v>62289</v>
+        <v>62595</v>
       </c>
       <c r="E320">
-        <v>75447</v>
+        <v>75616</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>38580</v>
       </c>
       <c r="C321">
-        <v>47398</v>
+        <v>47489</v>
       </c>
       <c r="D321">
-        <v>64251</v>
+        <v>64525</v>
       </c>
       <c r="E321">
-        <v>77106</v>
+        <v>77266</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>43009</v>
       </c>
       <c r="C322">
-        <v>55474</v>
+        <v>55491</v>
       </c>
       <c r="D322">
-        <v>74145</v>
+        <v>74161</v>
       </c>
       <c r="E322">
-        <v>85353</v>
+        <v>85364</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>37158</v>
       </c>
       <c r="C323">
-        <v>45590</v>
+        <v>45659</v>
       </c>
       <c r="D323">
-        <v>62094</v>
+        <v>62380</v>
       </c>
       <c r="E323">
-        <v>75015</v>
+        <v>75178</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>37158</v>
       </c>
       <c r="C324">
-        <v>45590</v>
+        <v>45659</v>
       </c>
       <c r="D324">
-        <v>62094</v>
+        <v>62380</v>
       </c>
       <c r="E324">
-        <v>75015</v>
+        <v>75178</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>37158</v>
       </c>
       <c r="C325">
-        <v>45590</v>
+        <v>45659</v>
       </c>
       <c r="D325">
-        <v>62094</v>
+        <v>62380</v>
       </c>
       <c r="E325">
-        <v>75015</v>
+        <v>75178</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>40935</v>
       </c>
       <c r="C326">
-        <v>49538</v>
+        <v>49610</v>
       </c>
       <c r="D326">
-        <v>65691</v>
+        <v>65940</v>
       </c>
       <c r="E326">
-        <v>78077</v>
+        <v>78229</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,10 +5913,10 @@
         <v>39271</v>
       </c>
       <c r="C327">
-        <v>51789</v>
+        <v>51797</v>
       </c>
       <c r="D327">
-        <v>70521</v>
+        <v>70544</v>
       </c>
       <c r="E327">
         <v>83015</v>
@@ -5930,13 +5930,13 @@
         <v>41354</v>
       </c>
       <c r="C328">
-        <v>53834</v>
+        <v>53839</v>
       </c>
       <c r="D328">
-        <v>72622</v>
+        <v>72639</v>
       </c>
       <c r="E328">
-        <v>83962</v>
+        <v>83972</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>38369</v>
       </c>
       <c r="C329">
-        <v>51305</v>
+        <v>51307</v>
       </c>
       <c r="D329">
-        <v>71051</v>
+        <v>71067</v>
       </c>
       <c r="E329">
-        <v>82961</v>
+        <v>82973</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>41354</v>
       </c>
       <c r="C330">
-        <v>53834</v>
+        <v>53839</v>
       </c>
       <c r="D330">
-        <v>72622</v>
+        <v>72639</v>
       </c>
       <c r="E330">
-        <v>83962</v>
+        <v>83972</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>35376</v>
       </c>
       <c r="C331">
-        <v>45698</v>
+        <v>45713</v>
       </c>
       <c r="D331">
-        <v>64497</v>
+        <v>64614</v>
       </c>
       <c r="E331">
-        <v>77084</v>
+        <v>77139</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,10 +5998,10 @@
         <v>41502</v>
       </c>
       <c r="C332">
-        <v>54591</v>
+        <v>54596</v>
       </c>
       <c r="D332">
-        <v>73809</v>
+        <v>73828</v>
       </c>
       <c r="E332">
         <v>85936</v>
@@ -6015,13 +6015,13 @@
         <v>38822</v>
       </c>
       <c r="C333">
-        <v>50562</v>
+        <v>50597</v>
       </c>
       <c r="D333">
-        <v>70664</v>
+        <v>70759</v>
       </c>
       <c r="E333">
-        <v>82947</v>
+        <v>83002</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,10 +6032,10 @@
         <v>45594</v>
       </c>
       <c r="C334">
-        <v>59717</v>
+        <v>59732</v>
       </c>
       <c r="D334">
-        <v>78399</v>
+        <v>78414</v>
       </c>
       <c r="E334">
         <v>89269</v>
@@ -6049,10 +6049,10 @@
         <v>43117</v>
       </c>
       <c r="C335">
-        <v>57416</v>
+        <v>57426</v>
       </c>
       <c r="D335">
-        <v>76967</v>
+        <v>76984</v>
       </c>
       <c r="E335">
         <v>88382</v>
@@ -6069,10 +6069,10 @@
         <v>53973</v>
       </c>
       <c r="D336">
-        <v>73648</v>
+        <v>73662</v>
       </c>
       <c r="E336">
-        <v>85107</v>
+        <v>85116</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6083,13 +6083,13 @@
         <v>11753</v>
       </c>
       <c r="C337">
-        <v>15942</v>
+        <v>15944</v>
       </c>
       <c r="D337">
-        <v>32219</v>
+        <v>32250</v>
       </c>
       <c r="E337">
-        <v>46945</v>
+        <v>46968</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6100,13 +6100,13 @@
         <v>10308</v>
       </c>
       <c r="C338">
-        <v>14454</v>
+        <v>14457</v>
       </c>
       <c r="D338">
-        <v>30541</v>
+        <v>30569</v>
       </c>
       <c r="E338">
-        <v>45108</v>
+        <v>45131</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6117,13 +6117,13 @@
         <v>11753</v>
       </c>
       <c r="C339">
-        <v>15942</v>
+        <v>15944</v>
       </c>
       <c r="D339">
-        <v>32219</v>
+        <v>32250</v>
       </c>
       <c r="E339">
-        <v>46945</v>
+        <v>46968</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>16779</v>
       </c>
       <c r="D340">
-        <v>35013</v>
+        <v>35015</v>
       </c>
       <c r="E340">
-        <v>51335</v>
+        <v>51339</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,7 +6154,7 @@
         <v>15934</v>
       </c>
       <c r="D341">
-        <v>33755</v>
+        <v>33759</v>
       </c>
       <c r="E341">
         <v>50453</v>
@@ -6168,13 +6168,13 @@
         <v>13450</v>
       </c>
       <c r="C342">
-        <v>19696</v>
+        <v>19699</v>
       </c>
       <c r="D342">
-        <v>39983</v>
+        <v>39986</v>
       </c>
       <c r="E342">
-        <v>57369</v>
+        <v>57375</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>13450</v>
       </c>
       <c r="C343">
-        <v>19696</v>
+        <v>19699</v>
       </c>
       <c r="D343">
-        <v>39983</v>
+        <v>39986</v>
       </c>
       <c r="E343">
-        <v>57369</v>
+        <v>57375</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>16779</v>
       </c>
       <c r="D344">
-        <v>35013</v>
+        <v>35015</v>
       </c>
       <c r="E344">
-        <v>51335</v>
+        <v>51339</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>13077</v>
       </c>
       <c r="D345">
-        <v>30087</v>
+        <v>30089</v>
       </c>
       <c r="E345">
-        <v>45242</v>
+        <v>45246</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>13077</v>
       </c>
       <c r="D346">
-        <v>30087</v>
+        <v>30089</v>
       </c>
       <c r="E346">
-        <v>45242</v>
+        <v>45246</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>13077</v>
       </c>
       <c r="D347">
-        <v>30087</v>
+        <v>30089</v>
       </c>
       <c r="E347">
-        <v>45242</v>
+        <v>45246</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6273,10 +6273,10 @@
         <v>19793</v>
       </c>
       <c r="D348">
-        <v>37599</v>
+        <v>37602</v>
       </c>
       <c r="E348">
-        <v>53800</v>
+        <v>53804</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6290,10 +6290,10 @@
         <v>19793</v>
       </c>
       <c r="D349">
-        <v>37599</v>
+        <v>37602</v>
       </c>
       <c r="E349">
-        <v>53800</v>
+        <v>53804</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6307,10 +6307,10 @@
         <v>19793</v>
       </c>
       <c r="D350">
-        <v>37599</v>
+        <v>37602</v>
       </c>
       <c r="E350">
-        <v>53800</v>
+        <v>53804</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6324,10 +6324,10 @@
         <v>11436</v>
       </c>
       <c r="D351">
-        <v>27509</v>
+        <v>27510</v>
       </c>
       <c r="E351">
-        <v>40885</v>
+        <v>40888</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6341,10 +6341,10 @@
         <v>11436</v>
       </c>
       <c r="D352">
-        <v>27509</v>
+        <v>27510</v>
       </c>
       <c r="E352">
-        <v>40885</v>
+        <v>40888</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6358,7 +6358,7 @@
         <v>25950</v>
       </c>
       <c r="D353">
-        <v>47427</v>
+        <v>47432</v>
       </c>
       <c r="E353">
         <v>65832</v>
@@ -6378,7 +6378,7 @@
         <v>41133</v>
       </c>
       <c r="E354">
-        <v>58274</v>
+        <v>58279</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6392,10 +6392,10 @@
         <v>26991</v>
       </c>
       <c r="D355">
-        <v>49163</v>
+        <v>49167</v>
       </c>
       <c r="E355">
-        <v>66852</v>
+        <v>66862</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6409,10 +6409,10 @@
         <v>19484</v>
       </c>
       <c r="D356">
-        <v>36940</v>
+        <v>36942</v>
       </c>
       <c r="E356">
-        <v>53558</v>
+        <v>53562</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6426,10 +6426,10 @@
         <v>19484</v>
       </c>
       <c r="D357">
-        <v>36940</v>
+        <v>36942</v>
       </c>
       <c r="E357">
-        <v>53558</v>
+        <v>53562</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6443,10 +6443,10 @@
         <v>19484</v>
       </c>
       <c r="D358">
-        <v>36940</v>
+        <v>36942</v>
       </c>
       <c r="E358">
-        <v>53558</v>
+        <v>53562</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6460,10 +6460,10 @@
         <v>12263</v>
       </c>
       <c r="D359">
-        <v>28613</v>
+        <v>28614</v>
       </c>
       <c r="E359">
-        <v>42690</v>
+        <v>42694</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6477,10 +6477,10 @@
         <v>12263</v>
       </c>
       <c r="D360">
-        <v>28613</v>
+        <v>28614</v>
       </c>
       <c r="E360">
-        <v>42690</v>
+        <v>42694</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6491,10 +6491,10 @@
         <v>24242</v>
       </c>
       <c r="C361">
-        <v>39340</v>
+        <v>39341</v>
       </c>
       <c r="D361">
-        <v>65601</v>
+        <v>65620</v>
       </c>
       <c r="E361">
         <v>81521</v>
@@ -6508,13 +6508,13 @@
         <v>23207</v>
       </c>
       <c r="C362">
-        <v>38982</v>
+        <v>38984</v>
       </c>
       <c r="D362">
-        <v>66304</v>
+        <v>66318</v>
       </c>
       <c r="E362">
-        <v>81450</v>
+        <v>81472</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>34571</v>
       </c>
       <c r="D363">
-        <v>62136</v>
+        <v>62142</v>
       </c>
       <c r="E363">
-        <v>78847</v>
+        <v>78859</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6542,13 +6542,13 @@
         <v>23950</v>
       </c>
       <c r="C364">
-        <v>39222</v>
+        <v>39231</v>
       </c>
       <c r="D364">
-        <v>65884</v>
+        <v>65904</v>
       </c>
       <c r="E364">
-        <v>81211</v>
+        <v>81233</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6559,13 +6559,13 @@
         <v>23950</v>
       </c>
       <c r="C365">
-        <v>39222</v>
+        <v>39231</v>
       </c>
       <c r="D365">
-        <v>65884</v>
+        <v>65904</v>
       </c>
       <c r="E365">
-        <v>81211</v>
+        <v>81233</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>18435</v>
       </c>
       <c r="C366">
-        <v>32991</v>
+        <v>32997</v>
       </c>
       <c r="D366">
-        <v>60499</v>
+        <v>60524</v>
       </c>
       <c r="E366">
-        <v>77342</v>
+        <v>77366</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6593,13 +6593,13 @@
         <v>18435</v>
       </c>
       <c r="C367">
-        <v>32991</v>
+        <v>32997</v>
       </c>
       <c r="D367">
-        <v>60499</v>
+        <v>60524</v>
       </c>
       <c r="E367">
-        <v>77342</v>
+        <v>77366</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6610,13 +6610,13 @@
         <v>19266</v>
       </c>
       <c r="C368">
-        <v>33693</v>
+        <v>33698</v>
       </c>
       <c r="D368">
-        <v>61082</v>
+        <v>61105</v>
       </c>
       <c r="E368">
-        <v>77805</v>
+        <v>77828</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6627,13 +6627,13 @@
         <v>18435</v>
       </c>
       <c r="C369">
-        <v>32991</v>
+        <v>32997</v>
       </c>
       <c r="D369">
-        <v>60499</v>
+        <v>60524</v>
       </c>
       <c r="E369">
-        <v>77342</v>
+        <v>77366</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>14235</v>
       </c>
       <c r="C370">
-        <v>27112</v>
+        <v>27113</v>
       </c>
       <c r="D370">
-        <v>55555</v>
+        <v>55562</v>
       </c>
       <c r="E370">
-        <v>73879</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>14235</v>
       </c>
       <c r="C371">
-        <v>27112</v>
+        <v>27113</v>
       </c>
       <c r="D371">
-        <v>55555</v>
+        <v>55562</v>
       </c>
       <c r="E371">
-        <v>73879</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>14235</v>
       </c>
       <c r="C372">
-        <v>27112</v>
+        <v>27113</v>
       </c>
       <c r="D372">
-        <v>55555</v>
+        <v>55562</v>
       </c>
       <c r="E372">
-        <v>73879</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6698,7 +6698,7 @@
         <v>31301</v>
       </c>
       <c r="D373">
-        <v>54747</v>
+        <v>54755</v>
       </c>
       <c r="E373">
         <v>71126</v>
@@ -6715,7 +6715,7 @@
         <v>23640</v>
       </c>
       <c r="D374">
-        <v>45983</v>
+        <v>45989</v>
       </c>
       <c r="E374">
         <v>64626</v>
@@ -6732,10 +6732,10 @@
         <v>32945</v>
       </c>
       <c r="D375">
-        <v>56873</v>
+        <v>56878</v>
       </c>
       <c r="E375">
-        <v>72171</v>
+        <v>72187</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>17682</v>
       </c>
       <c r="C376">
-        <v>25417</v>
+        <v>25418</v>
       </c>
       <c r="D376">
-        <v>48960</v>
+        <v>48964</v>
       </c>
       <c r="E376">
-        <v>66733</v>
+        <v>66743</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>17682</v>
       </c>
       <c r="C377">
-        <v>25417</v>
+        <v>25418</v>
       </c>
       <c r="D377">
-        <v>48960</v>
+        <v>48964</v>
       </c>
       <c r="E377">
-        <v>66733</v>
+        <v>66743</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6780,10 +6780,10 @@
         <v>25068</v>
       </c>
       <c r="C378">
-        <v>36924</v>
+        <v>36925</v>
       </c>
       <c r="D378">
-        <v>60380</v>
+        <v>60389</v>
       </c>
       <c r="E378">
         <v>75827</v>
@@ -6797,10 +6797,10 @@
         <v>25068</v>
       </c>
       <c r="C379">
-        <v>36924</v>
+        <v>36925</v>
       </c>
       <c r="D379">
-        <v>60380</v>
+        <v>60389</v>
       </c>
       <c r="E379">
         <v>75827</v>
@@ -6814,13 +6814,13 @@
         <v>26438</v>
       </c>
       <c r="C380">
-        <v>38793</v>
+        <v>38794</v>
       </c>
       <c r="D380">
-        <v>62582</v>
+        <v>62589</v>
       </c>
       <c r="E380">
-        <v>76826</v>
+        <v>76846</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6831,13 +6831,13 @@
         <v>26438</v>
       </c>
       <c r="C381">
-        <v>38793</v>
+        <v>38794</v>
       </c>
       <c r="D381">
-        <v>62582</v>
+        <v>62589</v>
       </c>
       <c r="E381">
-        <v>76826</v>
+        <v>76846</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>22725</v>
       </c>
       <c r="C382">
-        <v>33472</v>
+        <v>33473</v>
       </c>
       <c r="D382">
-        <v>57996</v>
+        <v>58004</v>
       </c>
       <c r="E382">
-        <v>73760</v>
+        <v>73778</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6865,13 +6865,13 @@
         <v>28621</v>
       </c>
       <c r="C383">
-        <v>42263</v>
+        <v>42264</v>
       </c>
       <c r="D383">
-        <v>65369</v>
+        <v>65381</v>
       </c>
       <c r="E383">
-        <v>78770</v>
+        <v>78791</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6885,10 +6885,10 @@
         <v>34909</v>
       </c>
       <c r="D384">
-        <v>59483</v>
+        <v>59491</v>
       </c>
       <c r="E384">
-        <v>74626</v>
+        <v>74645</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6899,13 +6899,13 @@
         <v>35405</v>
       </c>
       <c r="C385">
-        <v>49684</v>
+        <v>49688</v>
       </c>
       <c r="D385">
-        <v>70919</v>
+        <v>70937</v>
       </c>
       <c r="E385">
-        <v>82794</v>
+        <v>82813</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6919,10 +6919,10 @@
         <v>29427</v>
       </c>
       <c r="D386">
-        <v>54558</v>
+        <v>54564</v>
       </c>
       <c r="E386">
-        <v>71386</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6936,10 +6936,10 @@
         <v>29427</v>
       </c>
       <c r="D387">
-        <v>54558</v>
+        <v>54564</v>
       </c>
       <c r="E387">
-        <v>71386</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6967,13 +6967,13 @@
         <v>6019</v>
       </c>
       <c r="C389">
-        <v>9746</v>
+        <v>9747</v>
       </c>
       <c r="D389">
         <v>30283</v>
       </c>
       <c r="E389">
-        <v>50865</v>
+        <v>50867</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6984,13 +6984,13 @@
         <v>6019</v>
       </c>
       <c r="C390">
-        <v>9746</v>
+        <v>9747</v>
       </c>
       <c r="D390">
         <v>30283</v>
       </c>
       <c r="E390">
-        <v>50865</v>
+        <v>50867</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7018,13 +7018,13 @@
         <v>6019</v>
       </c>
       <c r="C392">
-        <v>9746</v>
+        <v>9747</v>
       </c>
       <c r="D392">
         <v>30283</v>
       </c>
       <c r="E392">
-        <v>50865</v>
+        <v>50867</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7072,10 +7072,10 @@
         <v>8331</v>
       </c>
       <c r="D395">
-        <v>23537</v>
+        <v>23538</v>
       </c>
       <c r="E395">
-        <v>38808</v>
+        <v>38809</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7089,10 +7089,10 @@
         <v>8331</v>
       </c>
       <c r="D396">
-        <v>23537</v>
+        <v>23538</v>
       </c>
       <c r="E396">
-        <v>38808</v>
+        <v>38809</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7109,7 +7109,7 @@
         <v>26514</v>
       </c>
       <c r="E397">
-        <v>43183</v>
+        <v>43184</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7126,7 +7126,7 @@
         <v>26514</v>
       </c>
       <c r="E398">
-        <v>43183</v>
+        <v>43184</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,7 +7140,7 @@
         <v>9003</v>
       </c>
       <c r="D399">
-        <v>32289</v>
+        <v>32290</v>
       </c>
       <c r="E399">
         <v>54836</v>
@@ -7157,10 +7157,10 @@
         <v>9079</v>
       </c>
       <c r="D400">
-        <v>33257</v>
+        <v>33258</v>
       </c>
       <c r="E400">
-        <v>55703</v>
+        <v>55708</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>9552</v>
       </c>
       <c r="D401">
-        <v>33690</v>
+        <v>33691</v>
       </c>
       <c r="E401">
-        <v>55868</v>
+        <v>55873</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7194,7 +7194,7 @@
         <v>30356</v>
       </c>
       <c r="E402">
-        <v>51761</v>
+        <v>51765</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>9079</v>
       </c>
       <c r="D403">
-        <v>33257</v>
+        <v>33258</v>
       </c>
       <c r="E403">
-        <v>55703</v>
+        <v>55708</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7228,7 +7228,7 @@
         <v>29201</v>
       </c>
       <c r="E404">
-        <v>50809</v>
+        <v>50813</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7245,7 +7245,7 @@
         <v>29201</v>
       </c>
       <c r="E405">
-        <v>50809</v>
+        <v>50813</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7262,7 +7262,7 @@
         <v>29201</v>
       </c>
       <c r="E406">
-        <v>50809</v>
+        <v>50813</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7279,7 +7279,7 @@
         <v>26488</v>
       </c>
       <c r="E407">
-        <v>47360</v>
+        <v>47362</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7296,7 +7296,7 @@
         <v>26488</v>
       </c>
       <c r="E408">
-        <v>47360</v>
+        <v>47362</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7313,7 +7313,7 @@
         <v>26488</v>
       </c>
       <c r="E409">
-        <v>47360</v>
+        <v>47362</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7324,10 +7324,10 @@
         <v>11583</v>
       </c>
       <c r="C410">
-        <v>24374</v>
+        <v>24377</v>
       </c>
       <c r="D410">
-        <v>53259</v>
+        <v>53275</v>
       </c>
       <c r="E410">
         <v>73573</v>
@@ -7344,10 +7344,10 @@
         <v>20106</v>
       </c>
       <c r="D411">
-        <v>49473</v>
+        <v>49481</v>
       </c>
       <c r="E411">
-        <v>70447</v>
+        <v>70465</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7361,10 +7361,10 @@
         <v>20106</v>
       </c>
       <c r="D412">
-        <v>49473</v>
+        <v>49481</v>
       </c>
       <c r="E412">
-        <v>70447</v>
+        <v>70465</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7378,10 +7378,10 @@
         <v>19481</v>
       </c>
       <c r="D413">
-        <v>48058</v>
+        <v>48065</v>
       </c>
       <c r="E413">
-        <v>68502</v>
+        <v>68519</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7392,13 +7392,13 @@
         <v>12655</v>
       </c>
       <c r="C414">
-        <v>26031</v>
+        <v>26033</v>
       </c>
       <c r="D414">
-        <v>55423</v>
+        <v>55439</v>
       </c>
       <c r="E414">
-        <v>74644</v>
+        <v>74666</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7412,10 +7412,10 @@
         <v>21418</v>
       </c>
       <c r="D415">
-        <v>50681</v>
+        <v>50690</v>
       </c>
       <c r="E415">
-        <v>71269</v>
+        <v>71288</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>21418</v>
       </c>
       <c r="D416">
-        <v>50681</v>
+        <v>50690</v>
       </c>
       <c r="E416">
-        <v>71269</v>
+        <v>71288</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7446,10 +7446,10 @@
         <v>14668</v>
       </c>
       <c r="D417">
-        <v>41560</v>
+        <v>41563</v>
       </c>
       <c r="E417">
-        <v>63215</v>
+        <v>63227</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7463,10 +7463,10 @@
         <v>14668</v>
       </c>
       <c r="D418">
-        <v>41560</v>
+        <v>41563</v>
       </c>
       <c r="E418">
-        <v>63215</v>
+        <v>63227</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,7 +7480,7 @@
         <v>19053</v>
       </c>
       <c r="D419">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E419">
         <v>63418</v>
@@ -7497,7 +7497,7 @@
         <v>19053</v>
       </c>
       <c r="D420">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E420">
         <v>63418</v>
@@ -7514,10 +7514,10 @@
         <v>15080</v>
       </c>
       <c r="D421">
-        <v>35935</v>
+        <v>35956</v>
       </c>
       <c r="E421">
-        <v>54155</v>
+        <v>54188</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>15080</v>
       </c>
       <c r="D422">
-        <v>35935</v>
+        <v>35956</v>
       </c>
       <c r="E422">
-        <v>54155</v>
+        <v>54188</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,7 +7548,7 @@
         <v>19053</v>
       </c>
       <c r="D423">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E423">
         <v>63418</v>
@@ -7565,7 +7565,7 @@
         <v>19053</v>
       </c>
       <c r="D424">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E424">
         <v>63418</v>
@@ -7582,10 +7582,10 @@
         <v>15080</v>
       </c>
       <c r="D425">
-        <v>35935</v>
+        <v>35956</v>
       </c>
       <c r="E425">
-        <v>54155</v>
+        <v>54188</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,7 +7599,7 @@
         <v>19053</v>
       </c>
       <c r="D426">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E426">
         <v>63418</v>
@@ -7616,10 +7616,10 @@
         <v>20152</v>
       </c>
       <c r="D427">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="E427">
-        <v>64453</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>20152</v>
       </c>
       <c r="D428">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="E428">
-        <v>64453</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,7 +7650,7 @@
         <v>19053</v>
       </c>
       <c r="D429">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E429">
         <v>63418</v>
@@ -7667,7 +7667,7 @@
         <v>19053</v>
       </c>
       <c r="D430">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E430">
         <v>63418</v>
@@ -7684,10 +7684,10 @@
         <v>15080</v>
       </c>
       <c r="D431">
-        <v>35935</v>
+        <v>35956</v>
       </c>
       <c r="E431">
-        <v>54155</v>
+        <v>54188</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,7 +7701,7 @@
         <v>19053</v>
       </c>
       <c r="D432">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E432">
         <v>63418</v>
@@ -7718,7 +7718,7 @@
         <v>19053</v>
       </c>
       <c r="D433">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E433">
         <v>63418</v>
@@ -7735,7 +7735,7 @@
         <v>13534</v>
       </c>
       <c r="D434">
-        <v>34715</v>
+        <v>34717</v>
       </c>
       <c r="E434">
         <v>54059</v>
@@ -7752,7 +7752,7 @@
         <v>19053</v>
       </c>
       <c r="D435">
-        <v>43489</v>
+        <v>43492</v>
       </c>
       <c r="E435">
         <v>63418</v>
@@ -7769,10 +7769,10 @@
         <v>14503</v>
       </c>
       <c r="D436">
-        <v>37047</v>
+        <v>37048</v>
       </c>
       <c r="E436">
-        <v>56063</v>
+        <v>56068</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>10247</v>
       </c>
       <c r="D437">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E437">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>10247</v>
       </c>
       <c r="D438">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E438">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>10247</v>
       </c>
       <c r="D439">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E439">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>10247</v>
       </c>
       <c r="D440">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E440">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>10247</v>
       </c>
       <c r="D441">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E441">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>9861</v>
       </c>
       <c r="D442">
-        <v>26719</v>
+        <v>26720</v>
       </c>
       <c r="E442">
-        <v>42499</v>
+        <v>42505</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>10247</v>
       </c>
       <c r="D443">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E443">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>10247</v>
       </c>
       <c r="D444">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E444">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>10247</v>
       </c>
       <c r="D445">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E445">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>10247</v>
       </c>
       <c r="D446">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E446">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>10247</v>
       </c>
       <c r="D447">
-        <v>28611</v>
+        <v>28612</v>
       </c>
       <c r="E447">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>28580</v>
       </c>
       <c r="D448">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E448">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>28580</v>
       </c>
       <c r="D449">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E449">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>28580</v>
       </c>
       <c r="D450">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E450">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>28580</v>
       </c>
       <c r="D451">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E451">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>28580</v>
       </c>
       <c r="D452">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E452">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>28580</v>
       </c>
       <c r="D453">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E453">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8075,10 +8075,10 @@
         <v>23018</v>
       </c>
       <c r="D454">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E454">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8092,10 +8092,10 @@
         <v>23018</v>
       </c>
       <c r="D455">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E455">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8109,10 +8109,10 @@
         <v>23018</v>
       </c>
       <c r="D456">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E456">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8126,10 +8126,10 @@
         <v>23018</v>
       </c>
       <c r="D457">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E457">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8143,10 +8143,10 @@
         <v>23018</v>
       </c>
       <c r="D458">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E458">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8160,10 +8160,10 @@
         <v>23018</v>
       </c>
       <c r="D459">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E459">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8177,10 +8177,10 @@
         <v>23018</v>
       </c>
       <c r="D460">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E460">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8194,10 +8194,10 @@
         <v>23018</v>
       </c>
       <c r="D461">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E461">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8211,10 +8211,10 @@
         <v>23018</v>
       </c>
       <c r="D462">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E462">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>20152</v>
       </c>
       <c r="D463">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="E463">
-        <v>64453</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>20152</v>
       </c>
       <c r="D464">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="E464">
-        <v>64453</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8262,7 +8262,7 @@
         <v>13534</v>
       </c>
       <c r="D465">
-        <v>34715</v>
+        <v>34717</v>
       </c>
       <c r="E465">
         <v>54059</v>
@@ -8279,10 +8279,10 @@
         <v>14241</v>
       </c>
       <c r="D466">
-        <v>36138</v>
+        <v>36139</v>
       </c>
       <c r="E466">
-        <v>55030</v>
+        <v>55034</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>20152</v>
       </c>
       <c r="D467">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="E467">
-        <v>64453</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>28580</v>
       </c>
       <c r="D468">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E468">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>28580</v>
       </c>
       <c r="D469">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E469">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>28580</v>
       </c>
       <c r="D470">
-        <v>53085</v>
+        <v>53086</v>
       </c>
       <c r="E470">
-        <v>70502</v>
+        <v>70508</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>20152</v>
       </c>
       <c r="D471">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="E471">
-        <v>64453</v>
+        <v>64462</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8381,10 +8381,10 @@
         <v>23018</v>
       </c>
       <c r="D472">
-        <v>48750</v>
+        <v>48751</v>
       </c>
       <c r="E472">
-        <v>67543</v>
+        <v>67551</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>14241</v>
       </c>
       <c r="D473">
-        <v>36138</v>
+        <v>36139</v>
       </c>
       <c r="E473">
-        <v>55030</v>
+        <v>55034</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>14241</v>
       </c>
       <c r="D474">
-        <v>36138</v>
+        <v>36139</v>
       </c>
       <c r="E474">
-        <v>55030</v>
+        <v>55034</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>14503</v>
       </c>
       <c r="D475">
-        <v>37047</v>
+        <v>37048</v>
       </c>
       <c r="E475">
-        <v>56063</v>
+        <v>56068</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>13350</v>
       </c>
       <c r="D476">
-        <v>35883</v>
+        <v>35884</v>
       </c>
       <c r="E476">
-        <v>54969</v>
+        <v>54973</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>13350</v>
       </c>
       <c r="D477">
-        <v>35883</v>
+        <v>35884</v>
       </c>
       <c r="E477">
-        <v>54969</v>
+        <v>54973</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8480,13 +8480,13 @@
         <v>8495</v>
       </c>
       <c r="C478">
-        <v>12573</v>
+        <v>12575</v>
       </c>
       <c r="D478">
-        <v>32870</v>
+        <v>32881</v>
       </c>
       <c r="E478">
-        <v>51505</v>
+        <v>51532</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8500,10 +8500,10 @@
         <v>14145</v>
       </c>
       <c r="D479">
-        <v>37522</v>
+        <v>37523</v>
       </c>
       <c r="E479">
-        <v>57649</v>
+        <v>57654</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8517,7 +8517,7 @@
         <v>15809</v>
       </c>
       <c r="D480">
-        <v>40062</v>
+        <v>40063</v>
       </c>
       <c r="E480">
         <v>60822</v>
@@ -8531,13 +8531,13 @@
         <v>8495</v>
       </c>
       <c r="C481">
-        <v>12573</v>
+        <v>12575</v>
       </c>
       <c r="D481">
-        <v>32870</v>
+        <v>32881</v>
       </c>
       <c r="E481">
-        <v>51505</v>
+        <v>51532</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8548,13 +8548,13 @@
         <v>8495</v>
       </c>
       <c r="C482">
-        <v>12573</v>
+        <v>12575</v>
       </c>
       <c r="D482">
-        <v>32870</v>
+        <v>32881</v>
       </c>
       <c r="E482">
-        <v>51505</v>
+        <v>51532</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8565,13 +8565,13 @@
         <v>8495</v>
       </c>
       <c r="C483">
-        <v>12573</v>
+        <v>12575</v>
       </c>
       <c r="D483">
-        <v>32870</v>
+        <v>32881</v>
       </c>
       <c r="E483">
-        <v>51505</v>
+        <v>51532</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8582,13 +8582,13 @@
         <v>8495</v>
       </c>
       <c r="C484">
-        <v>12573</v>
+        <v>12575</v>
       </c>
       <c r="D484">
-        <v>32870</v>
+        <v>32881</v>
       </c>
       <c r="E484">
-        <v>51505</v>
+        <v>51532</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8602,7 +8602,7 @@
         <v>15809</v>
       </c>
       <c r="D485">
-        <v>40062</v>
+        <v>40063</v>
       </c>
       <c r="E485">
         <v>60822</v>
@@ -8619,7 +8619,7 @@
         <v>15206</v>
       </c>
       <c r="D486">
-        <v>39063</v>
+        <v>39064</v>
       </c>
       <c r="E486">
         <v>59786</v>
@@ -8639,7 +8639,7 @@
         <v>36394</v>
       </c>
       <c r="E487">
-        <v>56061</v>
+        <v>56065</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8653,10 +8653,10 @@
         <v>14577</v>
       </c>
       <c r="D488">
-        <v>36893</v>
+        <v>36894</v>
       </c>
       <c r="E488">
-        <v>56235</v>
+        <v>56239</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8670,10 +8670,10 @@
         <v>14577</v>
       </c>
       <c r="D489">
-        <v>36893</v>
+        <v>36894</v>
       </c>
       <c r="E489">
-        <v>56235</v>
+        <v>56239</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8684,10 +8684,10 @@
         <v>13215</v>
       </c>
       <c r="C490">
-        <v>23602</v>
+        <v>23603</v>
       </c>
       <c r="D490">
-        <v>50442</v>
+        <v>50447</v>
       </c>
       <c r="E490">
         <v>70060</v>
@@ -8701,13 +8701,13 @@
         <v>14001</v>
       </c>
       <c r="C491">
-        <v>24988</v>
+        <v>24989</v>
       </c>
       <c r="D491">
-        <v>52432</v>
+        <v>52437</v>
       </c>
       <c r="E491">
-        <v>71045</v>
+        <v>71060</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8718,10 +8718,10 @@
         <v>13215</v>
       </c>
       <c r="C492">
-        <v>23602</v>
+        <v>23603</v>
       </c>
       <c r="D492">
-        <v>50442</v>
+        <v>50447</v>
       </c>
       <c r="E492">
         <v>70060</v>
@@ -8735,10 +8735,10 @@
         <v>13215</v>
       </c>
       <c r="C493">
-        <v>23602</v>
+        <v>23603</v>
       </c>
       <c r="D493">
-        <v>50442</v>
+        <v>50447</v>
       </c>
       <c r="E493">
         <v>70060</v>
@@ -8752,10 +8752,10 @@
         <v>13215</v>
       </c>
       <c r="C494">
-        <v>23602</v>
+        <v>23603</v>
       </c>
       <c r="D494">
-        <v>50442</v>
+        <v>50447</v>
       </c>
       <c r="E494">
         <v>70060</v>
@@ -8769,13 +8769,13 @@
         <v>14109</v>
       </c>
       <c r="C495">
-        <v>26649</v>
+        <v>26650</v>
       </c>
       <c r="D495">
-        <v>54708</v>
+        <v>54717</v>
       </c>
       <c r="E495">
-        <v>72895</v>
+        <v>72913</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,13 +8786,13 @@
         <v>16132</v>
       </c>
       <c r="C496">
-        <v>29448</v>
+        <v>29449</v>
       </c>
       <c r="D496">
-        <v>57100</v>
+        <v>57109</v>
       </c>
       <c r="E496">
-        <v>74553</v>
+        <v>74572</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>14109</v>
       </c>
       <c r="C497">
-        <v>26649</v>
+        <v>26650</v>
       </c>
       <c r="D497">
-        <v>54708</v>
+        <v>54717</v>
       </c>
       <c r="E497">
-        <v>72895</v>
+        <v>72913</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8823,10 +8823,10 @@
         <v>27387</v>
       </c>
       <c r="D498">
-        <v>52570</v>
+        <v>52575</v>
       </c>
       <c r="E498">
-        <v>69754</v>
+        <v>69770</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8840,10 +8840,10 @@
         <v>27387</v>
       </c>
       <c r="D499">
-        <v>52570</v>
+        <v>52575</v>
       </c>
       <c r="E499">
-        <v>69754</v>
+        <v>69770</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8857,10 +8857,10 @@
         <v>27387</v>
       </c>
       <c r="D500">
-        <v>52570</v>
+        <v>52575</v>
       </c>
       <c r="E500">
-        <v>69754</v>
+        <v>69770</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>16041</v>
       </c>
       <c r="D501">
-        <v>38388</v>
+        <v>38389</v>
       </c>
       <c r="E501">
-        <v>57828</v>
+        <v>57833</v>
       </c>
     </row>
   </sheetData>
